--- a/warmup_determination.xlsx
+++ b/warmup_determination.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b32c6e2a84854a2/Desktop/Edinburgh/University/Simulation/Simulation-Project-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_EEAECA480E3E71A760F6F602C73976629305E3ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{397AD199-7D09-4C84-9579-905B60A1B571}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_EEAECA480E3E71A760F6F602C73976629305E3ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{141961A2-6024-4B98-9A64-AD2F0D16959D}"/>
   <bookViews>
     <workbookView showSheetTabs="0" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,6 +65,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -387,6168 +391,6168 @@
   <dimension ref="A1:B11235"/>
   <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1">
-        <v>53.616051929999998</v>
-      </c>
-      <c r="B1">
-        <v>81.793612409999994</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>63.320412689999998</v>
-      </c>
-      <c r="B2">
-        <v>91.497973169999995</v>
-      </c>
-    </row>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>71.830631740000001</v>
+        <v>53.616051929999998</v>
       </c>
       <c r="B3">
-        <v>100.0081922</v>
+        <v>81.793612409999994</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>86.623023950000004</v>
+        <v>63.320412689999998</v>
       </c>
       <c r="B4">
-        <v>114.80058440000001</v>
+        <v>91.497973169999995</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>98.921557329999999</v>
+        <v>71.830631740000001</v>
       </c>
       <c r="B5">
-        <v>127.34964650000001</v>
+        <v>100.0081922</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>113.4848849</v>
+        <v>86.623023950000004</v>
       </c>
       <c r="B6">
-        <v>141.91297410000001</v>
+        <v>114.80058440000001</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>126.2743935</v>
+        <v>98.921557329999999</v>
       </c>
       <c r="B7">
-        <v>154.70248269999999</v>
+        <v>127.34964650000001</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>136.7197113</v>
+        <v>113.4848849</v>
       </c>
       <c r="B8">
-        <v>165.14780049999999</v>
+        <v>141.91297410000001</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>148.62249790000001</v>
+        <v>126.2743935</v>
       </c>
       <c r="B9">
-        <v>178.24345049999999</v>
+        <v>154.70248269999999</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>161.00167049999999</v>
+        <v>136.7197113</v>
       </c>
       <c r="B10">
-        <v>190.622623</v>
+        <v>165.14780049999999</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>171.5350052</v>
+        <v>148.62249790000001</v>
       </c>
       <c r="B11">
-        <v>201.15595769999999</v>
+        <v>178.24345049999999</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>181.09168489999999</v>
+        <v>161.00167049999999</v>
       </c>
       <c r="B12">
-        <v>210.71263740000001</v>
+        <v>190.622623</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>192.95117920000001</v>
+        <v>171.5350052</v>
       </c>
       <c r="B13">
-        <v>222.5721317</v>
+        <v>201.15595769999999</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>205.710532</v>
+        <v>181.09168489999999</v>
       </c>
       <c r="B14">
-        <v>235.33148460000001</v>
+        <v>210.71263740000001</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>215.05681240000001</v>
+        <v>192.95117920000001</v>
       </c>
       <c r="B15">
-        <v>246.82971309999999</v>
+        <v>222.5721317</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>228.47943749999999</v>
+        <v>205.710532</v>
       </c>
       <c r="B16">
-        <v>260.2523382</v>
+        <v>235.33148460000001</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>242.2603968</v>
+        <v>215.05681240000001</v>
       </c>
       <c r="B17">
-        <v>274.0332975</v>
+        <v>246.82971309999999</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>253.776748</v>
+        <v>228.47943749999999</v>
       </c>
       <c r="B18">
-        <v>285.54964869999998</v>
+        <v>260.2523382</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>264.57829429999998</v>
+        <v>242.2603968</v>
       </c>
       <c r="B19">
-        <v>297.7154294</v>
+        <v>274.0332975</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>277.5907401</v>
+        <v>253.776748</v>
       </c>
       <c r="B20">
-        <v>310.72787520000003</v>
+        <v>285.54964869999998</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>290.85067670000001</v>
+        <v>264.57829429999998</v>
       </c>
       <c r="B21">
-        <v>323.98781179999997</v>
+        <v>297.7154294</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>303.60578450000003</v>
+        <v>277.5907401</v>
       </c>
       <c r="B22">
-        <v>336.74291959999999</v>
+        <v>310.72787520000003</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>316.01702310000002</v>
+        <v>290.85067670000001</v>
       </c>
       <c r="B23">
-        <v>349.15415810000002</v>
+        <v>323.98781179999997</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>327.04358530000002</v>
+        <v>303.60578450000003</v>
       </c>
       <c r="B24">
-        <v>360.18072039999998</v>
+        <v>336.74291959999999</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>329.6168505</v>
+        <v>316.01702310000002</v>
       </c>
       <c r="B25">
-        <v>375.63066859999998</v>
+        <v>349.15415810000002</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>344.90832239999997</v>
+        <v>327.04358530000002</v>
       </c>
       <c r="B26">
-        <v>390.92214039999999</v>
+        <v>360.18072039999998</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>359.94766229999999</v>
+        <v>329.6168505</v>
       </c>
       <c r="B27">
-        <v>405.96148030000001</v>
+        <v>375.63066859999998</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>372.69500720000002</v>
+        <v>344.90832239999997</v>
       </c>
       <c r="B28">
-        <v>418.93154809999999</v>
+        <v>390.92214039999999</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>386.97274859999999</v>
+        <v>359.94766229999999</v>
       </c>
       <c r="B29">
-        <v>432.9865666</v>
+        <v>405.96148030000001</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>400.05313380000001</v>
+        <v>372.69500720000002</v>
       </c>
       <c r="B30">
-        <v>446.06695189999999</v>
+        <v>418.93154809999999</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>411.40150870000002</v>
+        <v>386.97274859999999</v>
       </c>
       <c r="B31">
-        <v>457.63804970000001</v>
+        <v>432.9865666</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>424.26431339999999</v>
+        <v>400.05313380000001</v>
       </c>
       <c r="B32">
-        <v>470.50085430000001</v>
+        <v>446.06695189999999</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>436.17246180000001</v>
+        <v>411.40150870000002</v>
       </c>
       <c r="B33">
-        <v>482.40900269999997</v>
+        <v>457.63804970000001</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>451.0798216</v>
+        <v>424.26431339999999</v>
       </c>
       <c r="B34">
-        <v>497.31636259999999</v>
+        <v>470.50085430000001</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>465.02538850000002</v>
+        <v>436.17246180000001</v>
       </c>
       <c r="B35">
-        <v>511.26192939999999</v>
+        <v>482.40900269999997</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>474.2664509</v>
+        <v>451.0798216</v>
       </c>
       <c r="B36">
-        <v>525.5112431</v>
+        <v>497.31636259999999</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>485.4105462</v>
+        <v>465.02538850000002</v>
       </c>
       <c r="B37">
-        <v>536.65533840000001</v>
+        <v>511.26192939999999</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>497.8083378</v>
+        <v>474.2664509</v>
       </c>
       <c r="B38">
-        <v>549.05313000000001</v>
+        <v>525.5112431</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>511.99236150000002</v>
+        <v>485.4105462</v>
       </c>
       <c r="B39">
-        <v>563.23715370000002</v>
+        <v>536.65533840000001</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>526.30527440000003</v>
+        <v>497.8083378</v>
       </c>
       <c r="B40">
-        <v>577.55006660000004</v>
+        <v>549.05313000000001</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>536.88950869999996</v>
+        <v>511.99236150000002</v>
       </c>
       <c r="B41">
-        <v>591.74493629999995</v>
+        <v>563.23715370000002</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>552.9554799</v>
+        <v>526.30527440000003</v>
       </c>
       <c r="B42">
-        <v>604.20027210000001</v>
+        <v>577.55006660000004</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>561.62267220000001</v>
+        <v>536.88950869999996</v>
       </c>
       <c r="B43">
-        <v>616.4780998</v>
+        <v>591.74493629999995</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>574.17231879999997</v>
+        <v>552.9554799</v>
       </c>
       <c r="B44">
-        <v>630.00502300000005</v>
+        <v>604.20027210000001</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>586.85180279999997</v>
+        <v>561.62267220000001</v>
       </c>
       <c r="B45">
-        <v>641.70723039999996</v>
+        <v>616.4780998</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>596.06363180000005</v>
+        <v>574.17231879999997</v>
       </c>
       <c r="B46">
-        <v>651.89633600000002</v>
+        <v>630.00502300000005</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>610.14912070000003</v>
+        <v>586.85180279999997</v>
       </c>
       <c r="B47">
-        <v>665.98182480000003</v>
+        <v>641.70723039999996</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>620.91943979999996</v>
+        <v>596.06363180000005</v>
       </c>
       <c r="B48">
-        <v>676.75214400000004</v>
+        <v>651.89633600000002</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>614.72736069999996</v>
+        <v>610.14912070000003</v>
       </c>
       <c r="B49">
-        <v>690.54732019999994</v>
+        <v>665.98182480000003</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>628.76016049999998</v>
+        <v>620.91943979999996</v>
       </c>
       <c r="B50">
-        <v>704.58011999999997</v>
+        <v>676.75214400000004</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>1205.972935</v>
+        <v>614.72736069999996</v>
       </c>
       <c r="B51">
-        <v>1281.7928939999999</v>
+        <v>690.54732019999994</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>1220.22273</v>
+        <v>628.76016049999998</v>
       </c>
       <c r="B52">
-        <v>1296.0426890000001</v>
+        <v>704.58011999999997</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>1229.6961349999999</v>
+        <v>1205.972935</v>
       </c>
       <c r="B53">
-        <v>1310.01404</v>
+        <v>1281.7928939999999</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>1242.6746680000001</v>
+        <v>1220.22273</v>
       </c>
       <c r="B54">
-        <v>1322.992573</v>
+        <v>1296.0426890000001</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>1255.8784089999999</v>
+        <v>1229.6961349999999</v>
       </c>
       <c r="B55">
-        <v>1336.196314</v>
+        <v>1310.01404</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>1271.3354670000001</v>
+        <v>1242.6746680000001</v>
       </c>
       <c r="B56">
-        <v>1351.6533710000001</v>
+        <v>1322.992573</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>1284.1954699999999</v>
+        <v>1255.8784089999999</v>
       </c>
       <c r="B57">
-        <v>1365.017654</v>
+        <v>1336.196314</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>1298.3301690000001</v>
+        <v>1271.3354670000001</v>
       </c>
       <c r="B58">
-        <v>1379.1523540000001</v>
+        <v>1351.6533710000001</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>1312.2618130000001</v>
+        <v>1284.1954699999999</v>
       </c>
       <c r="B59">
-        <v>1392.579718</v>
+        <v>1365.017654</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>1326.163317</v>
+        <v>1298.3301690000001</v>
       </c>
       <c r="B60">
-        <v>1406.985502</v>
+        <v>1379.1523540000001</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>1335.710118</v>
+        <v>1312.2618130000001</v>
       </c>
       <c r="B61">
-        <v>1416.532303</v>
+        <v>1392.579718</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>1347.246153</v>
+        <v>1326.163317</v>
       </c>
       <c r="B62">
-        <v>1428.068338</v>
+        <v>1406.985502</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>1358.114024</v>
+        <v>1335.710118</v>
       </c>
       <c r="B63">
-        <v>1440.734565</v>
+        <v>1416.532303</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>1372.7786860000001</v>
+        <v>1347.246153</v>
       </c>
       <c r="B64">
-        <v>1455.3992270000001</v>
+        <v>1428.068338</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>1385.7195959999999</v>
+        <v>1358.114024</v>
       </c>
       <c r="B65">
-        <v>1468.340136</v>
+        <v>1440.734565</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>1398.995905</v>
+        <v>1372.7786860000001</v>
       </c>
       <c r="B66">
-        <v>1481.6164450000001</v>
+        <v>1455.3992270000001</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>1413.056047</v>
+        <v>1385.7195959999999</v>
       </c>
       <c r="B67">
-        <v>1495.676588</v>
+        <v>1468.340136</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>1426.111373</v>
+        <v>1398.995905</v>
       </c>
       <c r="B68">
-        <v>1510.6792029999999</v>
+        <v>1481.6164450000001</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>1440.5394060000001</v>
+        <v>1413.056047</v>
       </c>
       <c r="B69">
-        <v>1525.1072360000001</v>
+        <v>1495.676588</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>1454.9290619999999</v>
+        <v>1426.111373</v>
       </c>
       <c r="B70">
-        <v>1539.4968919999999</v>
+        <v>1510.6792029999999</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>2175.6413109999999</v>
+        <v>1440.5394060000001</v>
       </c>
       <c r="B71">
-        <v>2261.8938889999999</v>
+        <v>1525.1072360000001</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>2186.896221</v>
+        <v>1454.9290619999999</v>
       </c>
       <c r="B72">
-        <v>2271.4640509999999</v>
+        <v>1539.4968919999999</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>2195.3807109999998</v>
+        <v>2175.6413109999999</v>
       </c>
       <c r="B73">
-        <v>2281.6332889999999</v>
+        <v>2261.8938889999999</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>2208.736159</v>
+        <v>2186.896221</v>
       </c>
       <c r="B74">
-        <v>2294.9887370000001</v>
+        <v>2271.4640509999999</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>2219.6007589999999</v>
+        <v>2195.3807109999998</v>
       </c>
       <c r="B75">
-        <v>2305.853337</v>
+        <v>2281.6332889999999</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>2231.9553940000001</v>
+        <v>2208.736159</v>
       </c>
       <c r="B76">
-        <v>2318.2079720000002</v>
+        <v>2294.9887370000001</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>2233.1202800000001</v>
+        <v>2219.6007589999999</v>
       </c>
       <c r="B77">
-        <v>2330.7728459999998</v>
+        <v>2305.853337</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>2243.7347119999999</v>
+        <v>2231.9553940000001</v>
       </c>
       <c r="B78">
-        <v>2341.3872780000002</v>
+        <v>2318.2079720000002</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>2253.9178980000002</v>
+        <v>2233.1202800000001</v>
       </c>
       <c r="B79">
-        <v>2351.570463</v>
+        <v>2330.7728459999998</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>2266.6450989999998</v>
+        <v>2243.7347119999999</v>
       </c>
       <c r="B80">
-        <v>2364.2976650000001</v>
+        <v>2341.3872780000002</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>2270.2612250000002</v>
+        <v>2253.9178980000002</v>
       </c>
       <c r="B81">
-        <v>2379.6833449999999</v>
+        <v>2351.570463</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>2291.2793069999998</v>
+        <v>2266.6450989999998</v>
       </c>
       <c r="B82">
-        <v>2388.9318720000001</v>
+        <v>2364.2976650000001</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>2292.832926</v>
+        <v>2270.2612250000002</v>
       </c>
       <c r="B83">
-        <v>2402.2550449999999</v>
+        <v>2379.6833449999999</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>2307.3437020000001</v>
+        <v>2291.2793069999998</v>
       </c>
       <c r="B84">
-        <v>2416.7658219999998</v>
+        <v>2388.9318720000001</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>2319.415082</v>
+        <v>2292.832926</v>
       </c>
       <c r="B85">
-        <v>2428.8372009999998</v>
+        <v>2402.2550449999999</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>2330.9367860000002</v>
+        <v>2307.3437020000001</v>
       </c>
       <c r="B86">
-        <v>2440.358905</v>
+        <v>2416.7658219999998</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>2345.1012649999998</v>
+        <v>2319.415082</v>
       </c>
       <c r="B87">
-        <v>2454.523385</v>
+        <v>2428.8372009999998</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>2332.1825920000001</v>
+        <v>2330.9367860000002</v>
       </c>
       <c r="B88">
-        <v>2463.5041670000001</v>
+        <v>2440.358905</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>2341.416193</v>
+        <v>2345.1012649999998</v>
       </c>
       <c r="B89">
-        <v>2472.737768</v>
+        <v>2454.523385</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>2354.5144289999998</v>
+        <v>2332.1825920000001</v>
       </c>
       <c r="B90">
-        <v>2485.8360039999998</v>
+        <v>2463.5041670000001</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>2366.8417570000001</v>
+        <v>2341.416193</v>
       </c>
       <c r="B91">
-        <v>2498.1633310000002</v>
+        <v>2472.737768</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>2380.1750630000001</v>
+        <v>2354.5144289999998</v>
       </c>
       <c r="B92">
-        <v>2511.4966380000001</v>
+        <v>2485.8360039999998</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>2393.1835609999998</v>
+        <v>2366.8417570000001</v>
       </c>
       <c r="B93">
-        <v>2526.673601</v>
+        <v>2498.1633310000002</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>2406.4430830000001</v>
+        <v>2380.1750630000001</v>
       </c>
       <c r="B94">
-        <v>2539.9331229999998</v>
+        <v>2511.4966380000001</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>2415.711159</v>
+        <v>2393.1835609999998</v>
       </c>
       <c r="B95">
-        <v>2549.2012</v>
+        <v>2526.673601</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>2427.9706470000001</v>
+        <v>2406.4430830000001</v>
       </c>
       <c r="B96">
-        <v>2561.4606880000001</v>
+        <v>2539.9331229999998</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>2439.1832690000001</v>
+        <v>2415.711159</v>
       </c>
       <c r="B97">
-        <v>2575.838479</v>
+        <v>2549.2012</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>2450.7295509999999</v>
+        <v>2427.9706470000001</v>
       </c>
       <c r="B98">
-        <v>2587.3847609999998</v>
+        <v>2561.4606880000001</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>2464.3317489999999</v>
+        <v>2439.1832690000001</v>
       </c>
       <c r="B99">
-        <v>2600.9869589999998</v>
+        <v>2575.838479</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>2479.90798</v>
+        <v>2450.7295509999999</v>
       </c>
       <c r="B100">
-        <v>2616.5631910000002</v>
+        <v>2587.3847609999998</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>2490.87844</v>
+        <v>2464.3317489999999</v>
       </c>
       <c r="B101">
-        <v>2627.5336499999999</v>
+        <v>2600.9869589999998</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>2492.5959579999999</v>
+        <v>2479.90798</v>
       </c>
       <c r="B102">
-        <v>2638.785464</v>
+        <v>2616.5631910000002</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>2504.094024</v>
+        <v>2490.87844</v>
       </c>
       <c r="B103">
-        <v>2650.2835300000002</v>
+        <v>2627.5336499999999</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>2517.7655329999998</v>
+        <v>2492.5959579999999</v>
       </c>
       <c r="B104">
-        <v>2663.9550380000001</v>
+        <v>2638.785464</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>2528.0629279999998</v>
+        <v>2504.094024</v>
       </c>
       <c r="B105">
-        <v>2674.252434</v>
+        <v>2650.2835300000002</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>2502.1317960000001</v>
+        <v>2517.7655329999998</v>
       </c>
       <c r="B106">
-        <v>2684.9010709999998</v>
+        <v>2663.9550380000001</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>2516.589575</v>
+        <v>2528.0629279999998</v>
       </c>
       <c r="B107">
-        <v>2699.3588500000001</v>
+        <v>2674.252434</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>2531.643309</v>
+        <v>2502.1317960000001</v>
       </c>
       <c r="B108">
-        <v>2714.4125840000002</v>
+        <v>2684.9010709999998</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>2542.8842639999998</v>
+        <v>2516.589575</v>
       </c>
       <c r="B109">
-        <v>2725.6535389999999</v>
+        <v>2699.3588500000001</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>2557.044437</v>
+        <v>2531.643309</v>
       </c>
       <c r="B110">
-        <v>2739.8137120000001</v>
+        <v>2714.4125840000002</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>2507.1838440000001</v>
+        <v>2542.8842639999998</v>
       </c>
       <c r="B111">
-        <v>2752.9951150000002</v>
+        <v>2725.6535389999999</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>2515.3613070000001</v>
+        <v>2557.044437</v>
       </c>
       <c r="B112">
-        <v>2761.1725780000002</v>
+        <v>2739.8137120000001</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113">
-        <v>2526.8723500000001</v>
+        <v>2507.1838440000001</v>
       </c>
       <c r="B113">
-        <v>2772.6836210000001</v>
+        <v>2752.9951150000002</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114">
-        <v>2540.2717280000002</v>
+        <v>2515.3613070000001</v>
       </c>
       <c r="B114">
-        <v>2786.0829990000002</v>
+        <v>2761.1725780000002</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115">
-        <v>2550.119976</v>
+        <v>2526.8723500000001</v>
       </c>
       <c r="B115">
-        <v>2795.931247</v>
+        <v>2772.6836210000001</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116">
-        <v>2510.2648949999998</v>
+        <v>2540.2717280000002</v>
       </c>
       <c r="B116">
-        <v>2804.5704780000001</v>
+        <v>2786.0829990000002</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117">
-        <v>2522.3666779999999</v>
+        <v>2550.119976</v>
       </c>
       <c r="B117">
-        <v>2816.6722610000002</v>
+        <v>2795.931247</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118">
-        <v>2534.77835</v>
+        <v>2510.2648949999998</v>
       </c>
       <c r="B118">
-        <v>2829.0839329999999</v>
+        <v>2804.5704780000001</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119">
-        <v>2479.7128250000001</v>
+        <v>2522.3666779999999</v>
       </c>
       <c r="B119">
-        <v>2844.9105300000001</v>
+        <v>2816.6722610000002</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>2613.1625770000001</v>
+        <v>2534.77835</v>
       </c>
       <c r="B120">
-        <v>2858.9738480000001</v>
+        <v>2829.0839329999999</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121">
-        <v>2508.8771040000001</v>
+        <v>2479.7128250000001</v>
       </c>
       <c r="B121">
-        <v>2874.0748090000002</v>
+        <v>2844.9105300000001</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>2521.673436</v>
+        <v>2613.1625770000001</v>
       </c>
       <c r="B122">
-        <v>2886.8711410000001</v>
+        <v>2858.9738480000001</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123">
-        <v>2535.9552359999998</v>
+        <v>2508.8771040000001</v>
       </c>
       <c r="B123">
-        <v>2901.1529409999998</v>
+        <v>2874.0748090000002</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124">
-        <v>2459.0995480000001</v>
+        <v>2521.673436</v>
       </c>
       <c r="B124">
-        <v>2913.3273089999998</v>
+        <v>2886.8711410000001</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125">
-        <v>2473.4629610000002</v>
+        <v>2535.9552359999998</v>
       </c>
       <c r="B125">
-        <v>2927.6907219999998</v>
+        <v>2901.1529409999998</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126">
-        <v>2572.5489499999999</v>
+        <v>2459.0995480000001</v>
       </c>
       <c r="B126">
-        <v>2937.7466549999999</v>
+        <v>2913.3273089999998</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127">
-        <v>2584.9024570000001</v>
+        <v>2473.4629610000002</v>
       </c>
       <c r="B127">
-        <v>2950.1001620000002</v>
+        <v>2927.6907219999998</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128">
-        <v>2510.011493</v>
+        <v>2572.5489499999999</v>
       </c>
       <c r="B128">
-        <v>2964.2392540000001</v>
+        <v>2937.7466549999999</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129">
-        <v>2524.1660870000001</v>
+        <v>2584.9024570000001</v>
       </c>
       <c r="B129">
-        <v>2978.3938480000002</v>
+        <v>2950.1001620000002</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130">
-        <v>2535.8791259999998</v>
+        <v>2510.011493</v>
       </c>
       <c r="B130">
-        <v>2990.1068869999999</v>
+        <v>2964.2392540000001</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131">
-        <v>2548.021839</v>
+        <v>2524.1660870000001</v>
       </c>
       <c r="B131">
-        <v>3002.2496000000001</v>
+        <v>2978.3938480000002</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132">
-        <v>2482.1052110000001</v>
+        <v>2535.8791259999998</v>
       </c>
       <c r="B132">
-        <v>3015.6437770000002</v>
+        <v>2990.1068869999999</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133">
-        <v>2496.4092690000002</v>
+        <v>2548.021839</v>
       </c>
       <c r="B133">
-        <v>3029.9478349999999</v>
+        <v>3002.2496000000001</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134">
-        <v>2508.912519</v>
+        <v>2482.1052110000001</v>
       </c>
       <c r="B134">
-        <v>3042.4510850000001</v>
+        <v>3015.6437770000002</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135">
-        <v>2522.8470349999998</v>
+        <v>2496.4092690000002</v>
       </c>
       <c r="B135">
-        <v>3056.385601</v>
+        <v>3029.9478349999999</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136">
-        <v>2534.236257</v>
+        <v>2508.912519</v>
       </c>
       <c r="B136">
-        <v>3067.7748219999999</v>
+        <v>3042.4510850000001</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137">
-        <v>2461.2896559999999</v>
+        <v>2522.8470349999998</v>
       </c>
       <c r="B137">
-        <v>3076.5237910000001</v>
+        <v>3056.385601</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138">
-        <v>2475.6514750000001</v>
+        <v>2534.236257</v>
       </c>
       <c r="B138">
-        <v>3090.8856099999998</v>
+        <v>3067.7748219999999</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139">
-        <v>2489.2865889999998</v>
+        <v>2461.2896559999999</v>
       </c>
       <c r="B139">
-        <v>3104.520724</v>
+        <v>3076.5237910000001</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140">
-        <v>2501.4087399999999</v>
+        <v>2475.6514750000001</v>
       </c>
       <c r="B140">
-        <v>3116.642875</v>
+        <v>3090.8856099999998</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141">
-        <v>3017.9005609999999</v>
+        <v>2489.2865889999998</v>
       </c>
       <c r="B141">
-        <v>3646.0154050000001</v>
+        <v>3104.520724</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142">
-        <v>3031.061588</v>
+        <v>2501.4087399999999</v>
       </c>
       <c r="B142">
-        <v>3659.1764309999999</v>
+        <v>3116.642875</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143">
-        <v>3041.367694</v>
+        <v>3017.9005609999999</v>
       </c>
       <c r="B143">
-        <v>3669.4825380000002</v>
+        <v>3646.0154050000001</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144">
-        <v>2996.27819</v>
+        <v>3031.061588</v>
       </c>
       <c r="B144">
-        <v>3682.0750499999999</v>
+        <v>3659.1764309999999</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145">
-        <v>3007.9889149999999</v>
+        <v>3041.367694</v>
       </c>
       <c r="B145">
-        <v>3693.7857749999998</v>
+        <v>3669.4825380000002</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146">
-        <v>3075.7220179999999</v>
+        <v>2996.27819</v>
       </c>
       <c r="B146">
-        <v>3703.8368620000001</v>
+        <v>3682.0750499999999</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147">
-        <v>3032.5710250000002</v>
+        <v>3007.9889149999999</v>
       </c>
       <c r="B147">
-        <v>3718.3678839999998</v>
+        <v>3693.7857749999998</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148">
-        <v>2422.1860919999999</v>
+        <v>3075.7220179999999</v>
       </c>
       <c r="B148">
-        <v>3731.9620490000002</v>
+        <v>3703.8368620000001</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149">
-        <v>2435.0392240000001</v>
+        <v>3032.5710250000002</v>
       </c>
       <c r="B149">
-        <v>3744.8151809999999</v>
+        <v>3718.3678839999998</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150">
-        <v>3071.8885460000001</v>
+        <v>2422.1860919999999</v>
       </c>
       <c r="B150">
-        <v>3757.6854060000001</v>
+        <v>3731.9620490000002</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151">
-        <v>2459.3576800000001</v>
+        <v>2435.0392240000001</v>
       </c>
       <c r="B151">
-        <v>3769.1336369999999</v>
+        <v>3744.8151809999999</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152">
-        <v>2471.6322599999999</v>
+        <v>3071.8885460000001</v>
       </c>
       <c r="B152">
-        <v>3781.4082170000001</v>
+        <v>3757.6854060000001</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153">
-        <v>2484.7244019999998</v>
+        <v>2459.3576800000001</v>
       </c>
       <c r="B153">
-        <v>3794.5003590000001</v>
+        <v>3769.1336369999999</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154">
-        <v>2497.1483189999999</v>
+        <v>2471.6322599999999</v>
       </c>
       <c r="B154">
-        <v>3806.9242760000002</v>
+        <v>3781.4082170000001</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155">
-        <v>2509.093265</v>
+        <v>2484.7244019999998</v>
       </c>
       <c r="B155">
-        <v>3818.8692219999998</v>
+        <v>3794.5003590000001</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156">
-        <v>2406.8717649999999</v>
+        <v>2497.1483189999999</v>
       </c>
       <c r="B156">
-        <v>3829.9654439999999</v>
+        <v>3806.9242760000002</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157">
-        <v>2418.5759830000002</v>
+        <v>2509.093265</v>
       </c>
       <c r="B157">
-        <v>3841.6696619999998</v>
+        <v>3818.8692219999998</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158">
-        <v>2432.4824079999999</v>
+        <v>2406.8717649999999</v>
       </c>
       <c r="B158">
-        <v>3855.5760869999999</v>
+        <v>3829.9654439999999</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159">
-        <v>2445.703133</v>
+        <v>2418.5759830000002</v>
       </c>
       <c r="B159">
-        <v>3868.7968110000002</v>
+        <v>3841.6696619999998</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160">
-        <v>2456.2112040000002</v>
+        <v>2432.4824079999999</v>
       </c>
       <c r="B160">
-        <v>3879.3048819999999</v>
+        <v>3855.5760869999999</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161">
-        <v>2470.7538760000002</v>
+        <v>2445.703133</v>
       </c>
       <c r="B161">
-        <v>3893.8475549999998</v>
+        <v>3868.7968110000002</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162">
-        <v>2460.028667</v>
+        <v>2456.2112040000002</v>
       </c>
       <c r="B162">
-        <v>3903.390042</v>
+        <v>3879.3048819999999</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163">
-        <v>2471.282005</v>
+        <v>2470.7538760000002</v>
       </c>
       <c r="B163">
-        <v>3914.64338</v>
+        <v>3893.8475549999998</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164">
-        <v>2483.5980679999998</v>
+        <v>2460.028667</v>
       </c>
       <c r="B164">
-        <v>3926.9594430000002</v>
+        <v>3903.390042</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165">
-        <v>2493.9970840000001</v>
+        <v>2471.282005</v>
       </c>
       <c r="B165">
-        <v>3937.358459</v>
+        <v>3914.64338</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166">
-        <v>2440.8299430000002</v>
+        <v>2483.5980679999998</v>
       </c>
       <c r="B166">
-        <v>3947.9970659999999</v>
+        <v>3926.9594430000002</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167">
-        <v>2455.2046140000002</v>
+        <v>2493.9970840000001</v>
       </c>
       <c r="B167">
-        <v>3962.3717369999999</v>
+        <v>3937.358459</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168">
-        <v>1689.895724</v>
+        <v>2440.8299430000002</v>
       </c>
       <c r="B168">
-        <v>3971.4213540000001</v>
+        <v>3947.9970659999999</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169">
-        <v>2477.1453980000001</v>
+        <v>2455.2046140000002</v>
       </c>
       <c r="B169">
-        <v>3984.3125209999998</v>
+        <v>3962.3717369999999</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170">
-        <v>2485.7180640000001</v>
+        <v>1689.895724</v>
       </c>
       <c r="B170">
-        <v>3992.8851869999999</v>
+        <v>3971.4213540000001</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171">
-        <v>1725.28442</v>
+        <v>2477.1453980000001</v>
       </c>
       <c r="B171">
-        <v>4006.81005</v>
+        <v>3984.3125209999998</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172">
-        <v>1735.95661</v>
+        <v>2485.7180640000001</v>
       </c>
       <c r="B172">
-        <v>4017.4822410000002</v>
+        <v>3992.8851869999999</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173">
-        <v>1750.5469680000001</v>
+        <v>1725.28442</v>
       </c>
       <c r="B173">
-        <v>4032.0725990000001</v>
+        <v>4006.81005</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174">
-        <v>1714.038914</v>
+        <v>1735.95661</v>
       </c>
       <c r="B174">
-        <v>4043.7837939999999</v>
+        <v>4017.4822410000002</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175">
-        <v>1726.162278</v>
+        <v>1750.5469680000001</v>
       </c>
       <c r="B175">
-        <v>4055.907158</v>
+        <v>4032.0725990000001</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176">
-        <v>1739.7869370000001</v>
+        <v>1714.038914</v>
       </c>
       <c r="B176">
-        <v>4069.531817</v>
+        <v>4043.7837939999999</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177">
-        <v>1754.12869</v>
+        <v>1726.162278</v>
       </c>
       <c r="B177">
-        <v>4083.8735700000002</v>
+        <v>4055.907158</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178">
-        <v>1764.867859</v>
+        <v>1739.7869370000001</v>
       </c>
       <c r="B178">
-        <v>4094.6127390000001</v>
+        <v>4069.531817</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179">
-        <v>1778.9170529999999</v>
+        <v>1754.12869</v>
       </c>
       <c r="B179">
-        <v>4108.6619330000003</v>
+        <v>4083.8735700000002</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180">
-        <v>1721.7737030000001</v>
+        <v>1764.867859</v>
       </c>
       <c r="B180">
-        <v>4122.1011330000001</v>
+        <v>4094.6127390000001</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181">
-        <v>1733.331981</v>
+        <v>1778.9170529999999</v>
       </c>
       <c r="B181">
-        <v>4133.6594109999996</v>
+        <v>4108.6619330000003</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182">
-        <v>1747.999446</v>
+        <v>1721.7737030000001</v>
       </c>
       <c r="B182">
-        <v>4148.3268760000001</v>
+        <v>4122.1011330000001</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183">
-        <v>1761.944518</v>
+        <v>1733.331981</v>
       </c>
       <c r="B183">
-        <v>4162.2719479999996</v>
+        <v>4133.6594109999996</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184">
-        <v>1775.8676499999999</v>
+        <v>1747.999446</v>
       </c>
       <c r="B184">
-        <v>4176.1950800000004</v>
+        <v>4148.3268760000001</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185">
-        <v>1721.684532</v>
+        <v>1761.944518</v>
       </c>
       <c r="B185">
-        <v>4189.1276340000004</v>
+        <v>4162.2719479999996</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186">
-        <v>1735.5506580000001</v>
+        <v>1775.8676499999999</v>
       </c>
       <c r="B186">
-        <v>4202.9937609999997</v>
+        <v>4176.1950800000004</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187">
-        <v>1746.954624</v>
+        <v>1721.684532</v>
       </c>
       <c r="B187">
-        <v>4214.3977269999996</v>
+        <v>4189.1276340000004</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188">
-        <v>1760.3347200000001</v>
+        <v>1735.5506580000001</v>
       </c>
       <c r="B188">
-        <v>4227.7778230000004</v>
+        <v>4202.9937609999997</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189">
-        <v>1771.3884350000001</v>
+        <v>1746.954624</v>
       </c>
       <c r="B189">
-        <v>4238.831537</v>
+        <v>4214.3977269999996</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190">
-        <v>1785.395031</v>
+        <v>1760.3347200000001</v>
       </c>
       <c r="B190">
-        <v>4252.8381339999996</v>
+        <v>4227.7778230000004</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191">
-        <v>1796.6682699999999</v>
+        <v>1771.3884350000001</v>
       </c>
       <c r="B191">
-        <v>4264.1113729999997</v>
+        <v>4238.831537</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192">
-        <v>1761.1165129999999</v>
+        <v>1785.395031</v>
       </c>
       <c r="B192">
-        <v>4277.6941720000004</v>
+        <v>4252.8381339999996</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193">
-        <v>1774.4618310000001</v>
+        <v>1796.6682699999999</v>
       </c>
       <c r="B193">
-        <v>4291.0394889999998</v>
+        <v>4264.1113729999997</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194">
-        <v>1783.4678839999999</v>
+        <v>1761.1165129999999</v>
       </c>
       <c r="B194">
-        <v>4300.0455419999998</v>
+        <v>4277.6941720000004</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195">
-        <v>1798.8740459999999</v>
+        <v>1774.4618310000001</v>
       </c>
       <c r="B195">
-        <v>4315.4517050000004</v>
+        <v>4291.0394889999998</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196">
-        <v>1813.5212839999999</v>
+        <v>1783.4678839999999</v>
       </c>
       <c r="B196">
-        <v>4330.098943</v>
+        <v>4300.0455419999998</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197">
-        <v>1824.722976</v>
+        <v>1798.8740459999999</v>
       </c>
       <c r="B197">
-        <v>4341.3006340000002</v>
+        <v>4315.4517050000004</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198">
-        <v>1723.786202</v>
+        <v>1813.5212839999999</v>
       </c>
       <c r="B198">
-        <v>4356.1459619999996</v>
+        <v>4330.098943</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199">
-        <v>1852.8304860000001</v>
+        <v>1824.722976</v>
       </c>
       <c r="B199">
-        <v>4369.4081450000003</v>
+        <v>4341.3006340000002</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200">
-        <v>1752.614198</v>
+        <v>1723.786202</v>
       </c>
       <c r="B200">
-        <v>4384.9739579999996</v>
+        <v>4356.1459619999996</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201">
-        <v>2281.929764</v>
+        <v>1852.8304860000001</v>
       </c>
       <c r="B201">
-        <v>4914.2895239999998</v>
+        <v>4369.4081450000003</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202">
-        <v>2297.0062849999999</v>
+        <v>1752.614198</v>
       </c>
       <c r="B202">
-        <v>4929.3660449999998</v>
+        <v>4384.9739579999996</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203">
-        <v>2306.9790119999998</v>
+        <v>2281.929764</v>
       </c>
       <c r="B203">
-        <v>4939.3387720000001</v>
+        <v>4914.2895239999998</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204">
-        <v>2264.7281790000002</v>
+        <v>2297.0062849999999</v>
       </c>
       <c r="B204">
-        <v>4951.1665300000004</v>
+        <v>4929.3660449999998</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205">
-        <v>2273.0175439999998</v>
+        <v>2306.9790119999998</v>
       </c>
       <c r="B205">
-        <v>4959.4558950000001</v>
+        <v>4939.3387720000001</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206">
-        <v>2283.7688870000002</v>
+        <v>2264.7281790000002</v>
       </c>
       <c r="B206">
-        <v>4970.207238</v>
+        <v>4951.1665300000004</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207">
-        <v>2298.9074420000002</v>
+        <v>2273.0175439999998</v>
       </c>
       <c r="B207">
-        <v>4985.3457930000004</v>
+        <v>4959.4558950000001</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208">
-        <v>2312.868121</v>
+        <v>2283.7688870000002</v>
       </c>
       <c r="B208">
-        <v>4999.3064720000002</v>
+        <v>4970.207238</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209">
-        <v>2265.8229889999998</v>
+        <v>2298.9074420000002</v>
       </c>
       <c r="B209">
-        <v>5012.9258630000004</v>
+        <v>4985.3457930000004</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210">
-        <v>2279.0741560000001</v>
+        <v>2312.868121</v>
       </c>
       <c r="B210">
-        <v>5026.1770310000002</v>
+        <v>4999.3064720000002</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211">
-        <v>2294.117127</v>
+        <v>2265.8229889999998</v>
       </c>
       <c r="B211">
-        <v>5041.220002</v>
+        <v>5012.9258630000004</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212">
-        <v>2307.8275870000002</v>
+        <v>2279.0741560000001</v>
       </c>
       <c r="B212">
-        <v>5054.9304620000003</v>
+        <v>5026.1770310000002</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213">
-        <v>2322.794848</v>
+        <v>2294.117127</v>
       </c>
       <c r="B213">
-        <v>5069.897723</v>
+        <v>5041.220002</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214">
-        <v>2201.3921909999999</v>
+        <v>2307.8275870000002</v>
       </c>
       <c r="B214">
-        <v>5084.0337419999996</v>
+        <v>5054.9304620000003</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215">
-        <v>2351.1541929999999</v>
+        <v>2322.794848</v>
       </c>
       <c r="B215">
-        <v>5098.2570679999999</v>
+        <v>5069.897723</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216">
-        <v>2227.9144689999998</v>
+        <v>2201.3921909999999</v>
       </c>
       <c r="B216">
-        <v>5110.55602</v>
+        <v>5084.0337419999996</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217">
-        <v>2237.722749</v>
+        <v>2351.1541929999999</v>
       </c>
       <c r="B217">
-        <v>5120.3643000000002</v>
+        <v>5098.2570679999999</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218">
-        <v>2249.965001</v>
+        <v>2227.9144689999998</v>
       </c>
       <c r="B218">
-        <v>5132.6065520000002</v>
+        <v>5110.55602</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219">
-        <v>2254.3692569999998</v>
+        <v>2237.722749</v>
       </c>
       <c r="B219">
-        <v>5146.7419719999998</v>
+        <v>5120.3643000000002</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220">
-        <v>2267.3961330000002</v>
+        <v>2249.965001</v>
       </c>
       <c r="B220">
-        <v>5159.7688479999997</v>
+        <v>5132.6065520000002</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221">
-        <v>2281.1939309999998</v>
+        <v>2254.3692569999998</v>
       </c>
       <c r="B221">
-        <v>5173.5666460000002</v>
+        <v>5146.7419719999998</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222">
-        <v>2295.1935819999999</v>
+        <v>2267.3961330000002</v>
       </c>
       <c r="B222">
-        <v>5187.5662970000003</v>
+        <v>5159.7688479999997</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223">
-        <v>2235.62086</v>
+        <v>2281.1939309999998</v>
       </c>
       <c r="B223">
-        <v>5201.2473790000004</v>
+        <v>5173.5666460000002</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224">
-        <v>2249.7041829999998</v>
+        <v>2295.1935819999999</v>
       </c>
       <c r="B224">
-        <v>5215.3307020000002</v>
+        <v>5187.5662970000003</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225">
-        <v>2262.633339</v>
+        <v>2235.62086</v>
       </c>
       <c r="B225">
-        <v>5228.2598580000003</v>
+        <v>5201.2473790000004</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226">
-        <v>2276.6411450000001</v>
+        <v>2249.7041829999998</v>
       </c>
       <c r="B226">
-        <v>5242.267664</v>
+        <v>5215.3307020000002</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227">
-        <v>2290.6643340000001</v>
+        <v>2262.633339</v>
       </c>
       <c r="B227">
-        <v>5256.2908530000004</v>
+        <v>5228.2598580000003</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228">
-        <v>2304.0446069999998</v>
+        <v>2276.6411450000001</v>
       </c>
       <c r="B228">
-        <v>5269.6711260000002</v>
+        <v>5242.267664</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229">
-        <v>2243.3190559999998</v>
+        <v>2290.6643340000001</v>
       </c>
       <c r="B229">
-        <v>5285.4739719999998</v>
+        <v>5256.2908530000004</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230">
-        <v>2253.445099</v>
+        <v>2304.0446069999998</v>
       </c>
       <c r="B230">
-        <v>5295.6000160000003</v>
+        <v>5269.6711260000002</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231">
-        <v>2263.8326050000001</v>
+        <v>2243.3190559999998</v>
       </c>
       <c r="B231">
-        <v>5305.9875220000004</v>
+        <v>5285.4739719999998</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232">
-        <v>2278.0680379999999</v>
+        <v>2253.445099</v>
       </c>
       <c r="B232">
-        <v>5320.2229539999998</v>
+        <v>5295.6000160000003</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233">
-        <v>2257.8710700000001</v>
+        <v>2263.8326050000001</v>
       </c>
       <c r="B233">
-        <v>5333.5252289999999</v>
+        <v>5305.9875220000004</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234">
-        <v>2268.2276860000002</v>
+        <v>2278.0680379999999</v>
       </c>
       <c r="B234">
-        <v>5343.8818439999995</v>
+        <v>5320.2229539999998</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235">
-        <v>2281.6908330000001</v>
+        <v>2257.8710700000001</v>
       </c>
       <c r="B235">
-        <v>5357.3449909999999</v>
+        <v>5333.5252289999999</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236">
-        <v>2229.2959540000002</v>
+        <v>2268.2276860000002</v>
       </c>
       <c r="B236">
-        <v>5368.8332689999997</v>
+        <v>5343.8818439999995</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237">
-        <v>2304.786642</v>
+        <v>2281.6908330000001</v>
       </c>
       <c r="B237">
-        <v>5380.4408000000003</v>
+        <v>5357.3449909999999</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238">
-        <v>2254.5684120000001</v>
+        <v>2229.2959540000002</v>
       </c>
       <c r="B238">
-        <v>5394.1057280000005</v>
+        <v>5368.8332689999997</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239">
-        <v>2267.5731730000002</v>
+        <v>2304.786642</v>
       </c>
       <c r="B239">
-        <v>5407.1104889999997</v>
+        <v>5380.4408000000003</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240">
-        <v>2282.8385969999999</v>
+        <v>2254.5684120000001</v>
       </c>
       <c r="B240">
-        <v>5422.3759120000004</v>
+        <v>5394.1057280000005</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241">
-        <v>2296.064194</v>
+        <v>2267.5731730000002</v>
       </c>
       <c r="B241">
-        <v>5435.6015100000004</v>
+        <v>5407.1104889999997</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242">
-        <v>1737.8080769999999</v>
+        <v>2282.8385969999999</v>
       </c>
       <c r="B242">
-        <v>5446.5519830000003</v>
+        <v>5422.3759120000004</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243">
-        <v>1753.216469</v>
+        <v>2296.064194</v>
       </c>
       <c r="B243">
-        <v>5461.9603749999997</v>
+        <v>5435.6015100000004</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244">
-        <v>1766.455565</v>
+        <v>1737.8080769999999</v>
       </c>
       <c r="B244">
-        <v>5475.1994709999999</v>
+        <v>5446.5519830000003</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245">
-        <v>1779.4924599999999</v>
+        <v>1753.216469</v>
       </c>
       <c r="B245">
-        <v>5488.2363660000001</v>
+        <v>5461.9603749999997</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246">
-        <v>1790.5636199999999</v>
+        <v>1766.455565</v>
       </c>
       <c r="B246">
-        <v>5499.3075269999999</v>
+        <v>5475.1994709999999</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247">
-        <v>1805.4772350000001</v>
+        <v>1779.4924599999999</v>
       </c>
       <c r="B247">
-        <v>5514.221141</v>
+        <v>5488.2363660000001</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248">
-        <v>1818.9098550000001</v>
+        <v>1790.5636199999999</v>
       </c>
       <c r="B248">
-        <v>5527.6537609999996</v>
+        <v>5499.3075269999999</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249">
-        <v>1714.9339620000001</v>
+        <v>1805.4772350000001</v>
       </c>
       <c r="B249">
-        <v>5542.8359170000003</v>
+        <v>5514.221141</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250">
-        <v>1729.8611960000001</v>
+        <v>1818.9098550000001</v>
       </c>
       <c r="B250">
-        <v>5557.7631510000001</v>
+        <v>5527.6537609999996</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251">
-        <v>2297.9583170000001</v>
+        <v>1714.9339620000001</v>
       </c>
       <c r="B251">
-        <v>6126.5920319999996</v>
+        <v>5542.8359170000003</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252">
-        <v>2323.4705389999999</v>
+        <v>1729.8611960000001</v>
       </c>
       <c r="B252">
-        <v>6152.1042539999999</v>
+        <v>5557.7631510000001</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253">
-        <v>2337.1370529999999</v>
+        <v>2297.9583170000001</v>
       </c>
       <c r="B253">
-        <v>6165.7707680000003</v>
+        <v>6126.5920319999996</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254">
-        <v>2350.6665790000002</v>
+        <v>2323.4705389999999</v>
       </c>
       <c r="B254">
-        <v>6179.3002939999997</v>
+        <v>6152.1042539999999</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255">
-        <v>2289.4457710000001</v>
+        <v>2337.1370529999999</v>
       </c>
       <c r="B255">
-        <v>6193.8437020000001</v>
+        <v>6165.7707680000003</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256">
-        <v>2375.70217</v>
+        <v>2350.6665790000002</v>
       </c>
       <c r="B256">
-        <v>6204.3358840000001</v>
+        <v>6179.3002939999997</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257">
-        <v>2310.6273200000001</v>
+        <v>2289.4457710000001</v>
       </c>
       <c r="B257">
-        <v>6215.025251</v>
+        <v>6193.8437020000001</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258">
-        <v>2325.1875879999998</v>
+        <v>2375.70217</v>
       </c>
       <c r="B258">
-        <v>6229.5855190000002</v>
+        <v>6204.3358840000001</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259">
-        <v>2324.2482759999998</v>
+        <v>2310.6273200000001</v>
       </c>
       <c r="B259">
-        <v>6239.4237229999999</v>
+        <v>6215.025251</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260">
-        <v>2350.8388610000002</v>
+        <v>2325.1875879999998</v>
       </c>
       <c r="B260">
-        <v>6255.2367919999997</v>
+        <v>6229.5855190000002</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261">
-        <v>2350.5967639999999</v>
+        <v>2324.2482759999998</v>
       </c>
       <c r="B261">
-        <v>6265.7722110000004</v>
+        <v>6239.4237229999999</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262">
-        <v>2375.8909060000001</v>
+        <v>2350.8388610000002</v>
       </c>
       <c r="B262">
-        <v>6280.2888370000001</v>
+        <v>6255.2367919999997</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263">
-        <v>2379.1545230000002</v>
+        <v>2350.5967639999999</v>
       </c>
       <c r="B263">
-        <v>6294.3299710000001</v>
+        <v>6265.7722110000004</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264">
-        <v>2393.5944920000002</v>
+        <v>2375.8909060000001</v>
       </c>
       <c r="B264">
-        <v>6308.7699389999998</v>
+        <v>6280.2888370000001</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265">
-        <v>2404.320373</v>
+        <v>2379.1545230000002</v>
       </c>
       <c r="B265">
-        <v>6319.4958200000001</v>
+        <v>6294.3299710000001</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266">
-        <v>2330.8767229999999</v>
+        <v>2393.5944920000002</v>
       </c>
       <c r="B266">
-        <v>6333.0493660000002</v>
+        <v>6308.7699389999998</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267">
-        <v>2428.6025599999998</v>
+        <v>2404.320373</v>
       </c>
       <c r="B267">
-        <v>6343.7780080000002</v>
+        <v>6319.4958200000001</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268">
-        <v>2356.200879</v>
+        <v>2330.8767229999999</v>
       </c>
       <c r="B268">
-        <v>6358.3735210000004</v>
+        <v>6333.0493660000002</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269">
-        <v>2368.9751080000001</v>
+        <v>2428.6025599999998</v>
       </c>
       <c r="B269">
-        <v>6371.1477500000001</v>
+        <v>6343.7780080000002</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270">
-        <v>2382.5565019999999</v>
+        <v>2356.200879</v>
       </c>
       <c r="B270">
-        <v>6384.7291439999999</v>
+        <v>6358.3735210000004</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271">
-        <v>2397.0077040000001</v>
+        <v>2368.9751080000001</v>
       </c>
       <c r="B271">
-        <v>6399.1803470000004</v>
+        <v>6371.1477500000001</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272">
-        <v>2369.167301</v>
+        <v>2382.5565019999999</v>
       </c>
       <c r="B272">
-        <v>6413.5023140000003</v>
+        <v>6384.7291439999999</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273">
-        <v>2381.3798069999998</v>
+        <v>2397.0077040000001</v>
       </c>
       <c r="B273">
-        <v>6425.7148200000001</v>
+        <v>6399.1803470000004</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274">
-        <v>2396.0795309999999</v>
+        <v>2369.167301</v>
       </c>
       <c r="B274">
-        <v>6440.4145440000002</v>
+        <v>6413.5023140000003</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275">
-        <v>2410.4305129999998</v>
+        <v>2381.3798069999998</v>
       </c>
       <c r="B275">
-        <v>6454.7655260000001</v>
+        <v>6425.7148200000001</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276">
-        <v>2425.833658</v>
+        <v>2396.0795309999999</v>
       </c>
       <c r="B276">
-        <v>6470.1686710000004</v>
+        <v>6440.4145440000002</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277">
-        <v>2350.6397689999999</v>
+        <v>2410.4305129999998</v>
       </c>
       <c r="B277">
-        <v>6484.5898129999996</v>
+        <v>6454.7655260000001</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278">
-        <v>2455.6748379999999</v>
+        <v>2425.833658</v>
       </c>
       <c r="B278">
-        <v>6500.0098509999998</v>
+        <v>6470.1686710000004</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279">
-        <v>2379.9666400000001</v>
+        <v>2350.6397689999999</v>
       </c>
       <c r="B279">
-        <v>6513.9166839999998</v>
+        <v>6484.5898129999996</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280">
-        <v>2392.323179</v>
+        <v>2455.6748379999999</v>
       </c>
       <c r="B280">
-        <v>6526.2732239999996</v>
+        <v>6500.0098509999998</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281">
-        <v>2404.850297</v>
+        <v>2379.9666400000001</v>
       </c>
       <c r="B281">
-        <v>6538.8003410000001</v>
+        <v>6513.9166839999998</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282">
-        <v>3094.8308860000002</v>
+        <v>2392.323179</v>
       </c>
       <c r="B282">
-        <v>7228.7809299999999</v>
+        <v>6526.2732239999996</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283">
-        <v>3104.4359319999999</v>
+        <v>2404.850297</v>
       </c>
       <c r="B283">
-        <v>7238.3859759999996</v>
+        <v>6538.8003410000001</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284">
-        <v>2956.890308</v>
+        <v>3094.8308860000002</v>
       </c>
       <c r="B284">
-        <v>7247.1818830000002</v>
+        <v>7228.7809299999999</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285">
-        <v>3125.630776</v>
+        <v>3104.4359319999999</v>
       </c>
       <c r="B285">
-        <v>7259.5808200000001</v>
+        <v>7238.3859759999996</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286">
-        <v>2982.9024469999999</v>
+        <v>2956.890308</v>
       </c>
       <c r="B286">
-        <v>7273.1940219999997</v>
+        <v>7247.1818830000002</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287">
-        <v>2995.2890560000001</v>
+        <v>3125.630776</v>
       </c>
       <c r="B287">
-        <v>7285.5806309999998</v>
+        <v>7259.5808200000001</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288">
-        <v>3006.66363</v>
+        <v>2982.9024469999999</v>
       </c>
       <c r="B288">
-        <v>7298.7863719999996</v>
+        <v>7273.1940219999997</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289">
-        <v>3018.6307769999999</v>
+        <v>2995.2890560000001</v>
       </c>
       <c r="B289">
-        <v>7308.9223519999996</v>
+        <v>7285.5806309999998</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290">
-        <v>3028.6268749999999</v>
+        <v>3006.66363</v>
       </c>
       <c r="B290">
-        <v>7318.9184500000001</v>
+        <v>7298.7863719999996</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291">
-        <v>3041.1414289999998</v>
+        <v>3018.6307769999999</v>
       </c>
       <c r="B291">
-        <v>7333.2641720000001</v>
+        <v>7308.9223519999996</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292">
-        <v>3053.9433760000002</v>
+        <v>3028.6268749999999</v>
       </c>
       <c r="B292">
-        <v>7346.0661179999997</v>
+        <v>7318.9184500000001</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293">
-        <v>3063.4961490000001</v>
+        <v>3041.1414289999998</v>
       </c>
       <c r="B293">
-        <v>7355.6188920000004</v>
+        <v>7333.2641720000001</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294">
-        <v>3074.8522419999999</v>
+        <v>3053.9433760000002</v>
       </c>
       <c r="B294">
-        <v>7366.9749849999998</v>
+        <v>7346.0661179999997</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295">
-        <v>3089.8844909999998</v>
+        <v>3063.4961490000001</v>
       </c>
       <c r="B295">
-        <v>7382.0072339999997</v>
+        <v>7355.6188920000004</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296">
-        <v>3008.4443030000002</v>
+        <v>3074.8522419999999</v>
       </c>
       <c r="B296">
-        <v>7393.04504</v>
+        <v>7366.9749849999998</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297">
-        <v>3019.879844</v>
+        <v>3089.8844909999998</v>
       </c>
       <c r="B297">
-        <v>7404.4805809999998</v>
+        <v>7382.0072339999997</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298">
-        <v>2471.6235799999999</v>
+        <v>3008.4443030000002</v>
       </c>
       <c r="B298">
-        <v>7418.8950180000002</v>
+        <v>7393.04504</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299">
-        <v>3046.5273299999999</v>
+        <v>3019.879844</v>
       </c>
       <c r="B299">
-        <v>7431.1280660000002</v>
+        <v>7404.4805809999998</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300">
-        <v>2496.8100930000001</v>
+        <v>2471.6235799999999</v>
       </c>
       <c r="B300">
-        <v>7444.0815309999998</v>
+        <v>7418.8950180000002</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301">
-        <v>2510.4787409999999</v>
+        <v>3046.5273299999999</v>
       </c>
       <c r="B301">
-        <v>7457.7501789999997</v>
+        <v>7431.1280660000002</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302">
-        <v>2521.9881599999999</v>
+        <v>2496.8100930000001</v>
       </c>
       <c r="B302">
-        <v>7469.2595979999996</v>
+        <v>7444.0815309999998</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303">
-        <v>2535.6944360000002</v>
+        <v>2510.4787409999999</v>
       </c>
       <c r="B303">
-        <v>7482.9658740000004</v>
+        <v>7457.7501789999997</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304">
-        <v>2544.088534</v>
+        <v>2521.9881599999999</v>
       </c>
       <c r="B304">
-        <v>7491.3599720000002</v>
+        <v>7469.2595979999996</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305">
-        <v>2558.72829</v>
+        <v>2535.6944360000002</v>
       </c>
       <c r="B305">
-        <v>7505.9997279999998</v>
+        <v>7482.9658740000004</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306">
-        <v>2514.646174</v>
+        <v>2544.088534</v>
       </c>
       <c r="B306">
-        <v>7519.8328780000002</v>
+        <v>7491.3599720000002</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307">
-        <v>2529.1018239999999</v>
+        <v>2558.72829</v>
       </c>
       <c r="B307">
-        <v>7534.288528</v>
+        <v>7505.9997279999998</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308">
-        <v>2542.1653139999999</v>
+        <v>2514.646174</v>
       </c>
       <c r="B308">
-        <v>7547.3520179999996</v>
+        <v>7519.8328780000002</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309">
-        <v>2554.7647339999999</v>
+        <v>2529.1018239999999</v>
       </c>
       <c r="B309">
-        <v>7559.9514380000001</v>
+        <v>7534.288528</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310">
-        <v>2569.0093029999998</v>
+        <v>2542.1653139999999</v>
       </c>
       <c r="B310">
-        <v>7574.1960079999999</v>
+        <v>7547.3520179999996</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311">
-        <v>2584.2641359999998</v>
+        <v>2554.7647339999999</v>
       </c>
       <c r="B311">
-        <v>7589.4508400000004</v>
+        <v>7559.9514380000001</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312">
-        <v>2496.4304590000002</v>
+        <v>2569.0093029999998</v>
       </c>
       <c r="B312">
-        <v>7601.8585650000005</v>
+        <v>7574.1960079999999</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313">
-        <v>2507.8243069999999</v>
+        <v>2584.2641359999998</v>
       </c>
       <c r="B313">
-        <v>7613.2524139999996</v>
+        <v>7589.4508400000004</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314">
-        <v>2522.0149470000001</v>
+        <v>2496.4304590000002</v>
       </c>
       <c r="B314">
-        <v>7627.443053</v>
+        <v>7601.8585650000005</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315">
-        <v>2535.6767759999998</v>
+        <v>2507.8243069999999</v>
       </c>
       <c r="B315">
-        <v>7641.1048819999996</v>
+        <v>7613.2524139999996</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316">
-        <v>2511.0074730000001</v>
+        <v>2522.0149470000001</v>
       </c>
       <c r="B316">
-        <v>7655.1014279999999</v>
+        <v>7627.443053</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317">
-        <v>2560.870715</v>
+        <v>2535.6767759999998</v>
       </c>
       <c r="B317">
-        <v>7666.2988219999997</v>
+        <v>7641.1048819999996</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318">
-        <v>2534.4748070000001</v>
+        <v>2511.0074730000001</v>
       </c>
       <c r="B318">
-        <v>7678.5687619999999</v>
+        <v>7655.1014279999999</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319">
-        <v>2547.4036930000002</v>
+        <v>2560.870715</v>
       </c>
       <c r="B319">
-        <v>7691.4976479999996</v>
+        <v>7666.2988219999997</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320">
-        <v>2557.7768099999998</v>
+        <v>2534.4748070000001</v>
       </c>
       <c r="B320">
-        <v>7701.870766</v>
+        <v>7678.5687619999999</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321">
-        <v>2504.980239</v>
+        <v>2547.4036930000002</v>
       </c>
       <c r="B321">
-        <v>7716.7478769999998</v>
+        <v>7691.4976479999996</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322">
-        <v>2583.5453550000002</v>
+        <v>2557.7768099999998</v>
       </c>
       <c r="B322">
-        <v>7727.6393109999999</v>
+        <v>7701.870766</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323">
-        <v>2527.846716</v>
+        <v>2504.980239</v>
       </c>
       <c r="B323">
-        <v>7739.6143540000003</v>
+        <v>7716.7478769999998</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324">
-        <v>2473.3229719999999</v>
+        <v>2583.5453550000002</v>
       </c>
       <c r="B324">
-        <v>7752.0745070000003</v>
+        <v>7727.6393109999999</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325">
-        <v>2488.3409729999998</v>
+        <v>2527.846716</v>
       </c>
       <c r="B325">
-        <v>7767.0925090000001</v>
+        <v>7739.6143540000003</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326">
-        <v>2497.9191689999998</v>
+        <v>2473.3229719999999</v>
       </c>
       <c r="B326">
-        <v>7776.6707050000005</v>
+        <v>7752.0745070000003</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327">
-        <v>2509.3383039999999</v>
+        <v>2488.3409729999998</v>
       </c>
       <c r="B327">
-        <v>7788.0898390000002</v>
+        <v>7767.0925090000001</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328">
-        <v>2522.7853960000002</v>
+        <v>2497.9191689999998</v>
       </c>
       <c r="B328">
-        <v>7801.536932</v>
+        <v>7776.6707050000005</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329">
-        <v>2533.3054739999998</v>
+        <v>2509.3383039999999</v>
       </c>
       <c r="B329">
-        <v>7812.0570100000004</v>
+        <v>7788.0898390000002</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330">
-        <v>2499.8379749999999</v>
+        <v>2522.7853960000002</v>
       </c>
       <c r="B330">
-        <v>7827.240033</v>
+        <v>7801.536932</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331">
-        <v>2514.3373219999999</v>
+        <v>2533.3054739999998</v>
       </c>
       <c r="B331">
-        <v>7841.73938</v>
+        <v>7812.0570100000004</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332">
-        <v>2529.410742</v>
+        <v>2499.8379749999999</v>
       </c>
       <c r="B332">
-        <v>7856.8127999999997</v>
+        <v>7827.240033</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333">
-        <v>2540.3258900000001</v>
+        <v>2514.3373219999999</v>
       </c>
       <c r="B333">
-        <v>7867.7279479999997</v>
+        <v>7841.73938</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334">
-        <v>2495.4350290000002</v>
+        <v>2529.410742</v>
       </c>
       <c r="B334">
-        <v>7883.1218760000002</v>
+        <v>7856.8127999999997</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335">
-        <v>2509.692775</v>
+        <v>2540.3258900000001</v>
       </c>
       <c r="B335">
-        <v>7897.3796220000004</v>
+        <v>7867.7279479999997</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336">
-        <v>2522.0574729999998</v>
+        <v>2495.4350290000002</v>
       </c>
       <c r="B336">
-        <v>7909.7443210000001</v>
+        <v>7883.1218760000002</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337">
-        <v>2537.1867510000002</v>
+        <v>2509.692775</v>
       </c>
       <c r="B337">
-        <v>7924.8735980000001</v>
+        <v>7897.3796220000004</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338">
-        <v>2550.977421</v>
+        <v>2522.0574729999998</v>
       </c>
       <c r="B338">
-        <v>7938.6642680000004</v>
+        <v>7909.7443210000001</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339">
-        <v>2565.1176909999999</v>
+        <v>2537.1867510000002</v>
       </c>
       <c r="B339">
-        <v>7952.8045380000003</v>
+        <v>7924.8735980000001</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340">
-        <v>2579.4746369999998</v>
+        <v>2550.977421</v>
       </c>
       <c r="B340">
-        <v>7967.1614840000002</v>
+        <v>7938.6642680000004</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341">
-        <v>2536.8558910000002</v>
+        <v>2565.1176909999999</v>
       </c>
       <c r="B341">
-        <v>7980.7220440000001</v>
+        <v>7952.8045380000003</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342">
-        <v>2547.8521139999998</v>
+        <v>2579.4746369999998</v>
       </c>
       <c r="B342">
-        <v>7991.7182679999996</v>
+        <v>7967.1614840000002</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343">
-        <v>2560.955993</v>
+        <v>2536.8558910000002</v>
       </c>
       <c r="B343">
-        <v>8004.8221460000004</v>
+        <v>7980.7220440000001</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344">
-        <v>2570.0320980000001</v>
+        <v>2547.8521139999998</v>
       </c>
       <c r="B344">
-        <v>8013.898252</v>
+        <v>7991.7182679999996</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345">
-        <v>2583.7380410000001</v>
+        <v>2560.955993</v>
       </c>
       <c r="B345">
-        <v>8027.6041939999996</v>
+        <v>8004.8221460000004</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346">
-        <v>2593.8476300000002</v>
+        <v>2570.0320980000001</v>
       </c>
       <c r="B346">
-        <v>8037.7137839999996</v>
+        <v>8013.898252</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347">
-        <v>2512.9629829999999</v>
+        <v>2583.7380410000001</v>
       </c>
       <c r="B347">
-        <v>8051.406688</v>
+        <v>8027.6041939999996</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348">
-        <v>2525.0641009999999</v>
+        <v>2593.8476300000002</v>
       </c>
       <c r="B348">
-        <v>8063.5078059999996</v>
+        <v>8037.7137839999996</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349">
-        <v>2539.4970349999999</v>
+        <v>2512.9629829999999</v>
       </c>
       <c r="B349">
-        <v>8077.94074</v>
+        <v>8051.406688</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350">
-        <v>2553.3226829999999</v>
+        <v>2525.0641009999999</v>
       </c>
       <c r="B350">
-        <v>8091.7663890000003</v>
+        <v>8063.5078059999996</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351">
-        <v>2348.5437000000002</v>
+        <v>2539.4970349999999</v>
       </c>
       <c r="B351">
-        <v>8558.2816550000007</v>
+        <v>8077.94074</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352">
-        <v>2401.104413</v>
+        <v>2553.3226829999999</v>
       </c>
       <c r="B352">
-        <v>8610.8423679999996</v>
+        <v>8091.7663890000003</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353">
-        <v>2412.4027769999998</v>
+        <v>2348.5437000000002</v>
       </c>
       <c r="B353">
-        <v>8622.1407309999995</v>
+        <v>8558.2816550000007</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354">
-        <v>2420.9663799999998</v>
+        <v>2401.104413</v>
       </c>
       <c r="B354">
-        <v>8630.7043350000004</v>
+        <v>8610.8423679999996</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355">
-        <v>2432.4952090000002</v>
+        <v>2412.4027769999998</v>
       </c>
       <c r="B355">
-        <v>8642.2331639999993</v>
+        <v>8622.1407309999995</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356">
-        <v>2442.8622930000001</v>
+        <v>2420.9663799999998</v>
       </c>
       <c r="B356">
-        <v>8652.6002470000003</v>
+        <v>8630.7043350000004</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357">
-        <v>2375.980967</v>
+        <v>2432.4952090000002</v>
       </c>
       <c r="B357">
-        <v>8666.6458970000003</v>
+        <v>8642.2331639999993</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358">
-        <v>2391.4670839999999</v>
+        <v>2442.8622930000001</v>
       </c>
       <c r="B358">
-        <v>8682.1320140000007</v>
+        <v>8652.6002470000003</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359">
-        <v>2339.6621190000001</v>
+        <v>2375.980967</v>
       </c>
       <c r="B359">
-        <v>8694.4475239999992</v>
+        <v>8666.6458970000003</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360">
-        <v>2417.1863320000002</v>
+        <v>2391.4670839999999</v>
       </c>
       <c r="B360">
-        <v>8707.8512620000001</v>
+        <v>8682.1320140000007</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361">
-        <v>2366.4457389999998</v>
+        <v>2339.6621190000001</v>
       </c>
       <c r="B361">
-        <v>8721.2311430000009</v>
+        <v>8694.4475239999992</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362">
-        <v>2444.8156509999999</v>
+        <v>2417.1863320000002</v>
       </c>
       <c r="B362">
-        <v>8735.4805809999998</v>
+        <v>8707.8512620000001</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363">
-        <v>2390.732403</v>
+        <v>2366.4457389999998</v>
       </c>
       <c r="B363">
-        <v>8745.5178070000002</v>
+        <v>8721.2311430000009</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364">
-        <v>2403.2476459999998</v>
+        <v>2444.8156509999999</v>
       </c>
       <c r="B364">
-        <v>8758.03305</v>
+        <v>8735.4805809999998</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365">
-        <v>2416.5485629999998</v>
+        <v>2390.732403</v>
       </c>
       <c r="B365">
-        <v>8771.3339670000005</v>
+        <v>8745.5178070000002</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366">
-        <v>2430.0223590000001</v>
+        <v>2403.2476459999998</v>
       </c>
       <c r="B366">
-        <v>8784.8077639999992</v>
+        <v>8758.03305</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367">
-        <v>2374.200245</v>
+        <v>2416.5485629999998</v>
       </c>
       <c r="B367">
-        <v>8798.5629449999997</v>
+        <v>8771.3339670000005</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368">
-        <v>2384.4024669999999</v>
+        <v>2430.0223590000001</v>
       </c>
       <c r="B368">
-        <v>8808.7651679999999</v>
+        <v>8784.8077639999992</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369">
-        <v>2396.9445810000002</v>
+        <v>2374.200245</v>
       </c>
       <c r="B369">
-        <v>8821.3072819999998</v>
+        <v>8798.5629449999997</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370">
-        <v>2405.7988140000002</v>
+        <v>2384.4024669999999</v>
       </c>
       <c r="B370">
-        <v>8830.1615149999998</v>
+        <v>8808.7651679999999</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371">
-        <v>2419.8491170000002</v>
+        <v>2396.9445810000002</v>
       </c>
       <c r="B371">
-        <v>8844.2118179999998</v>
+        <v>8821.3072819999998</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372">
-        <v>2432.2986040000001</v>
+        <v>2405.7988140000002</v>
       </c>
       <c r="B372">
-        <v>8856.6613049999996</v>
+        <v>8830.1615149999998</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373">
-        <v>2356.040207</v>
+        <v>2419.8491170000002</v>
       </c>
       <c r="B373">
-        <v>8869.7816089999997</v>
+        <v>8844.2118179999998</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374">
-        <v>2368.694105</v>
+        <v>2432.2986040000001</v>
       </c>
       <c r="B374">
-        <v>8882.4355080000005</v>
+        <v>8856.6613049999996</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375">
-        <v>2381.597843</v>
+        <v>2356.040207</v>
       </c>
       <c r="B375">
-        <v>8895.3392449999992</v>
+        <v>8869.7816089999997</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376">
-        <v>2393.6250190000001</v>
+        <v>2368.694105</v>
       </c>
       <c r="B376">
-        <v>8907.3664219999991</v>
+        <v>8882.4355080000005</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377">
-        <v>2406.7100610000002</v>
+        <v>2381.597843</v>
       </c>
       <c r="B377">
-        <v>8920.4514639999998</v>
+        <v>8895.3392449999992</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378">
-        <v>1651.9778899999999</v>
+        <v>2393.6250190000001</v>
       </c>
       <c r="B378">
-        <v>8931.9257199999993</v>
+        <v>8907.3664219999991</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379">
-        <v>1665.9560389999999</v>
+        <v>2406.7100610000002</v>
       </c>
       <c r="B379">
-        <v>8945.9038689999998</v>
+        <v>8920.4514639999998</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380">
-        <v>1675.27242</v>
+        <v>1651.9778899999999</v>
       </c>
       <c r="B380">
-        <v>8955.2202500000003</v>
+        <v>8931.9257199999993</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381">
-        <v>1689.3721840000001</v>
+        <v>1665.9560389999999</v>
       </c>
       <c r="B381">
-        <v>8969.3200140000008</v>
+        <v>8945.9038689999998</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382">
-        <v>1703.907584</v>
+        <v>1675.27242</v>
       </c>
       <c r="B382">
-        <v>8983.8554139999997</v>
+        <v>8955.2202500000003</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383">
-        <v>1716.4240050000001</v>
+        <v>1689.3721840000001</v>
       </c>
       <c r="B383">
-        <v>8997.0773790000003</v>
+        <v>8969.3200140000008</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384">
-        <v>1730.4508860000001</v>
+        <v>1703.907584</v>
       </c>
       <c r="B384">
-        <v>9011.1042600000001</v>
+        <v>8983.8554139999997</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385">
-        <v>1743.9262450000001</v>
+        <v>1716.4240050000001</v>
       </c>
       <c r="B385">
-        <v>9024.5796200000004</v>
+        <v>8997.0773790000003</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386">
-        <v>1756.9276850000001</v>
+        <v>1730.4508860000001</v>
       </c>
       <c r="B386">
-        <v>9037.5810590000001</v>
+        <v>9011.1042600000001</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387">
-        <v>1770.7187220000001</v>
+        <v>1743.9262450000001</v>
       </c>
       <c r="B387">
-        <v>9051.3720959999991</v>
+        <v>9024.5796200000004</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388">
-        <v>1736.2892400000001</v>
+        <v>1756.9276850000001</v>
       </c>
       <c r="B388">
-        <v>9065.8603779999994</v>
+        <v>9037.5810590000001</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389">
-        <v>1747.6789309999999</v>
+        <v>1770.7187220000001</v>
       </c>
       <c r="B389">
-        <v>9077.2500689999997</v>
+        <v>9051.3720959999991</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390">
-        <v>1760.7080000000001</v>
+        <v>1736.2892400000001</v>
       </c>
       <c r="B390">
-        <v>9090.2791369999995</v>
+        <v>9065.8603779999994</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391">
-        <v>1772.080618</v>
+        <v>1747.6789309999999</v>
       </c>
       <c r="B391">
-        <v>9101.6517550000008</v>
+        <v>9077.2500689999997</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392">
-        <v>1696.4963029999999</v>
+        <v>1760.7080000000001</v>
       </c>
       <c r="B392">
-        <v>9113.7433089999995</v>
+        <v>9090.2791369999995</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393">
-        <v>1711.721507</v>
+        <v>1772.080618</v>
       </c>
       <c r="B393">
-        <v>9128.9685129999998</v>
+        <v>9101.6517550000008</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394">
-        <v>1725.8939869999999</v>
+        <v>1696.4963029999999</v>
       </c>
       <c r="B394">
-        <v>9143.1409930000009</v>
+        <v>9113.7433089999995</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395">
-        <v>1738.3790409999999</v>
+        <v>1711.721507</v>
       </c>
       <c r="B395">
-        <v>9155.6260459999994</v>
+        <v>9128.9685129999998</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396">
-        <v>1679.666236</v>
+        <v>1725.8939869999999</v>
       </c>
       <c r="B396">
-        <v>9169.1774979999991</v>
+        <v>9143.1409930000009</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397">
-        <v>1693.658009</v>
+        <v>1738.3790409999999</v>
       </c>
       <c r="B397">
-        <v>9183.1692719999992</v>
+        <v>9155.6260459999994</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398">
-        <v>1705.6982720000001</v>
+        <v>1679.666236</v>
       </c>
       <c r="B398">
-        <v>9195.209535</v>
+        <v>9169.1774979999991</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399">
-        <v>1718.0936400000001</v>
+        <v>1693.658009</v>
       </c>
       <c r="B399">
-        <v>9207.6049029999995</v>
+        <v>9183.1692719999992</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400">
-        <v>1678.930891</v>
+        <v>1705.6982720000001</v>
       </c>
       <c r="B400">
-        <v>9220.067438</v>
+        <v>9195.209535</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401">
-        <v>2238.8806530000002</v>
+        <v>1718.0936400000001</v>
       </c>
       <c r="B401">
-        <v>9780.0172000000002</v>
+        <v>9207.6049029999995</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402">
-        <v>2253.5455390000002</v>
+        <v>1678.930891</v>
       </c>
       <c r="B402">
-        <v>9794.6820860000007</v>
+        <v>9220.067438</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403">
-        <v>2268.5238920000002</v>
+        <v>2238.8806530000002</v>
       </c>
       <c r="B403">
-        <v>9809.6604399999997</v>
+        <v>9780.0172000000002</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404">
-        <v>2279.4563910000002</v>
+        <v>2253.5455390000002</v>
       </c>
       <c r="B404">
-        <v>9829.2814639999997</v>
+        <v>9794.6820860000007</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405">
-        <v>2304.7327740000001</v>
+        <v>2268.5238920000002</v>
       </c>
       <c r="B405">
-        <v>9854.557847</v>
+        <v>9809.6604399999997</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406">
-        <v>2318.779282</v>
+        <v>2279.4563910000002</v>
       </c>
       <c r="B406">
-        <v>9868.6043549999995</v>
+        <v>9829.2814639999997</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407">
-        <v>2336.5095040000001</v>
+        <v>2304.7327740000001</v>
       </c>
       <c r="B407">
-        <v>9877.6460509999997</v>
+        <v>9854.557847</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408">
-        <v>2338.3522440000002</v>
+        <v>2318.779282</v>
       </c>
       <c r="B408">
-        <v>9888.1773169999997</v>
+        <v>9868.6043549999995</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409">
-        <v>2292.0833980000002</v>
+        <v>2336.5095040000001</v>
       </c>
       <c r="B409">
-        <v>9898.709503</v>
+        <v>9877.6460509999997</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410">
-        <v>2362.7162069999999</v>
+        <v>2338.3522440000002</v>
       </c>
       <c r="B410">
-        <v>9912.5412799999995</v>
+        <v>9888.1773169999997</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411">
-        <v>2318.4865119999999</v>
+        <v>2292.0833980000002</v>
       </c>
       <c r="B411">
-        <v>9925.1126170000007</v>
+        <v>9898.709503</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412">
-        <v>2331.2789240000002</v>
+        <v>2362.7162069999999</v>
       </c>
       <c r="B412">
-        <v>9937.9050289999996</v>
+        <v>9912.5412799999995</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413">
-        <v>2345.208881</v>
+        <v>2318.4865119999999</v>
       </c>
       <c r="B413">
-        <v>9951.8349859999998</v>
+        <v>9925.1126170000007</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414">
-        <v>2276.67931</v>
+        <v>2331.2789240000002</v>
       </c>
       <c r="B414">
-        <v>9964.2849129999995</v>
+        <v>9937.9050289999996</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415">
-        <v>2425.5154689999999</v>
+        <v>2345.208881</v>
       </c>
       <c r="B415">
-        <v>9975.3405419999999</v>
+        <v>9951.8349859999998</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416">
-        <v>2302.7688189999999</v>
+        <v>2276.67931</v>
       </c>
       <c r="B416">
-        <v>9990.3744220000008</v>
+        <v>9964.2849129999995</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417">
-        <v>2316.743774</v>
+        <v>2425.5154689999999</v>
       </c>
       <c r="B417">
-        <v>10004.34938</v>
+        <v>9975.3405419999999</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418">
-        <v>2411.6696010000001</v>
+        <v>2302.7688189999999</v>
       </c>
       <c r="B418">
-        <v>10018.29571</v>
+        <v>9990.3744220000008</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419">
-        <v>2341.0549310000001</v>
+        <v>2316.743774</v>
       </c>
       <c r="B419">
-        <v>10028.660529999999</v>
+        <v>10004.34938</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420">
-        <v>2306.0516739999998</v>
+        <v>2411.6696010000001</v>
       </c>
       <c r="B420">
-        <v>10043.15733</v>
+        <v>10018.29571</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421">
-        <v>3098.31176</v>
+        <v>2341.0549310000001</v>
       </c>
       <c r="B421">
-        <v>10785.917359999999</v>
+        <v>10028.660529999999</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422">
-        <v>3057.4190950000002</v>
+        <v>2306.0516739999998</v>
       </c>
       <c r="B422">
-        <v>10794.52475</v>
+        <v>10043.15733</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423">
-        <v>3071.6004910000001</v>
+        <v>3098.31176</v>
       </c>
       <c r="B423">
-        <v>10808.70615</v>
+        <v>10785.917359999999</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424">
-        <v>3085.5136900000002</v>
+        <v>3057.4190950000002</v>
       </c>
       <c r="B424">
-        <v>10822.619350000001</v>
+        <v>10794.52475</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425">
-        <v>3094.7334380000002</v>
+        <v>3071.6004910000001</v>
       </c>
       <c r="B425">
-        <v>10831.839099999999</v>
+        <v>10808.70615</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426">
-        <v>3029.3856030000002</v>
+        <v>3085.5136900000002</v>
       </c>
       <c r="B426">
-        <v>10846.46859</v>
+        <v>10822.619350000001</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427">
-        <v>3119.6800130000001</v>
+        <v>3094.7334380000002</v>
       </c>
       <c r="B427">
-        <v>10856.785669999999</v>
+        <v>10831.839099999999</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428">
-        <v>3053.6910539999999</v>
+        <v>3029.3856030000002</v>
       </c>
       <c r="B428">
-        <v>10870.77404</v>
+        <v>10846.46859</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429">
-        <v>3067.830575</v>
+        <v>3119.6800130000001</v>
       </c>
       <c r="B429">
-        <v>10884.913560000001</v>
+        <v>10856.785669999999</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430">
-        <v>3081.1734510000001</v>
+        <v>3053.6910539999999</v>
       </c>
       <c r="B430">
-        <v>10898.256429999999</v>
+        <v>10870.77404</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431">
-        <v>3094.8574060000001</v>
+        <v>3067.830575</v>
       </c>
       <c r="B431">
-        <v>10911.94039</v>
+        <v>10884.913560000001</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432">
-        <v>3109.2610800000002</v>
+        <v>3081.1734510000001</v>
       </c>
       <c r="B432">
-        <v>10926.344059999999</v>
+        <v>10898.256429999999</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433">
-        <v>2945.7476339999998</v>
+        <v>3094.8574060000001</v>
       </c>
       <c r="B433">
-        <v>10936.647269999999</v>
+        <v>10911.94039</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434">
-        <v>2959.2324440000002</v>
+        <v>3109.2610800000002</v>
       </c>
       <c r="B434">
-        <v>10950.132079999999</v>
+        <v>10926.344059999999</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435">
-        <v>3145.1149759999998</v>
+        <v>2945.7476339999998</v>
       </c>
       <c r="B435">
-        <v>10962.19796</v>
+        <v>10936.647269999999</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436">
-        <v>2983.4894789999998</v>
+        <v>2959.2324440000002</v>
       </c>
       <c r="B436">
-        <v>10974.38911</v>
+        <v>10950.132079999999</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437">
-        <v>2997.0358289999999</v>
+        <v>3145.1149759999998</v>
       </c>
       <c r="B437">
-        <v>10987.935460000001</v>
+        <v>10962.19796</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438">
-        <v>3007.306908</v>
+        <v>2983.4894789999998</v>
       </c>
       <c r="B438">
-        <v>10998.206539999999</v>
+        <v>10974.38911</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439">
-        <v>3017.8239490000001</v>
+        <v>2997.0358289999999</v>
       </c>
       <c r="B439">
-        <v>11010.753500000001</v>
+        <v>10987.935460000001</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440">
-        <v>3032.568867</v>
+        <v>3007.306908</v>
       </c>
       <c r="B440">
-        <v>11025.49842</v>
+        <v>10998.206539999999</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441">
-        <v>3046.3357409999999</v>
+        <v>3017.8239490000001</v>
       </c>
       <c r="B441">
-        <v>11037.23537</v>
+        <v>11010.753500000001</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442">
-        <v>3057.1004659999999</v>
+        <v>3032.568867</v>
       </c>
       <c r="B442">
-        <v>11050.03001</v>
+        <v>11025.49842</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443">
-        <v>3068.1809290000001</v>
+        <v>3046.3357409999999</v>
       </c>
       <c r="B443">
-        <v>11061.110479999999</v>
+        <v>11037.23537</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444">
-        <v>3026.1735749999998</v>
+        <v>3057.1004659999999</v>
       </c>
       <c r="B444">
-        <v>11075.334699999999</v>
+        <v>11050.03001</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445">
-        <v>3040.0652679999998</v>
+        <v>3068.1809290000001</v>
       </c>
       <c r="B445">
-        <v>11089.22639</v>
+        <v>11061.110479999999</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446">
-        <v>2999.4601520000001</v>
+        <v>3026.1735749999998</v>
       </c>
       <c r="B446">
-        <v>11100.556350000001</v>
+        <v>11075.334699999999</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447">
-        <v>3121.5545459999998</v>
+        <v>3040.0652679999998</v>
       </c>
       <c r="B447">
-        <v>11114.48409</v>
+        <v>11089.22639</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448">
-        <v>3077.923816</v>
+        <v>2999.4601520000001</v>
       </c>
       <c r="B448">
-        <v>11127.084940000001</v>
+        <v>11100.556350000001</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449">
-        <v>3037.3012020000001</v>
+        <v>3121.5545459999998</v>
       </c>
       <c r="B449">
-        <v>11138.3974</v>
+        <v>11114.48409</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450">
-        <v>3103.2370430000001</v>
+        <v>3077.923816</v>
       </c>
       <c r="B450">
-        <v>11152.39817</v>
+        <v>11127.084940000001</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451">
-        <v>3063.5342879999998</v>
+        <v>3037.3012020000001</v>
       </c>
       <c r="B451">
-        <v>11164.63049</v>
+        <v>11138.3974</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452">
-        <v>3075.3144010000001</v>
+        <v>3103.2370430000001</v>
       </c>
       <c r="B452">
-        <v>11176.410599999999</v>
+        <v>11152.39817</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453">
-        <v>3089.995359</v>
+        <v>3063.5342879999998</v>
       </c>
       <c r="B453">
-        <v>11191.091560000001</v>
+        <v>11164.63049</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454">
-        <v>2544.14851</v>
+        <v>3075.3144010000001</v>
       </c>
       <c r="B454">
-        <v>11204.36573</v>
+        <v>11176.410599999999</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455">
-        <v>2555.2499389999998</v>
+        <v>3089.995359</v>
       </c>
       <c r="B455">
-        <v>11215.46716</v>
+        <v>11191.091560000001</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456">
-        <v>2567.2872050000001</v>
+        <v>2544.14851</v>
       </c>
       <c r="B456">
-        <v>11227.504430000001</v>
+        <v>11204.36573</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457">
-        <v>2577.91939</v>
+        <v>2555.2499389999998</v>
       </c>
       <c r="B457">
-        <v>11238.13661</v>
+        <v>11215.46716</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458">
-        <v>2499.4014099999999</v>
+        <v>2567.2872050000001</v>
       </c>
       <c r="B458">
-        <v>11251.66437</v>
+        <v>11227.504430000001</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459">
-        <v>2603.3056879999999</v>
+        <v>2577.91939</v>
       </c>
       <c r="B459">
-        <v>11263.52291</v>
+        <v>11238.13661</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460">
-        <v>2523.310348</v>
+        <v>2499.4014099999999</v>
       </c>
       <c r="B460">
-        <v>11275.5733</v>
+        <v>11251.66437</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461">
-        <v>2533.2354850000002</v>
+        <v>2603.3056879999999</v>
       </c>
       <c r="B461">
-        <v>11285.498439999999</v>
+        <v>11263.52291</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462">
-        <v>2544.2262500000002</v>
+        <v>2523.310348</v>
       </c>
       <c r="B462">
-        <v>11296.48921</v>
+        <v>11275.5733</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463">
-        <v>2558.7723609999998</v>
+        <v>2533.2354850000002</v>
       </c>
       <c r="B463">
-        <v>11311.035320000001</v>
+        <v>11285.498439999999</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464">
-        <v>2525.4482800000001</v>
+        <v>2544.2262500000002</v>
       </c>
       <c r="B464">
-        <v>11321.043830000001</v>
+        <v>11296.48921</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465">
-        <v>2535.6701539999999</v>
+        <v>2558.7723609999998</v>
       </c>
       <c r="B465">
-        <v>11331.26571</v>
+        <v>11311.035320000001</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466">
-        <v>2458.9452849999998</v>
+        <v>2525.4482800000001</v>
       </c>
       <c r="B466">
-        <v>11344.70217</v>
+        <v>11321.043830000001</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467">
-        <v>2559.9486139999999</v>
+        <v>2535.6701539999999</v>
       </c>
       <c r="B467">
-        <v>11355.544169999999</v>
+        <v>11331.26571</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468">
-        <v>2483.1114680000001</v>
+        <v>2458.9452849999998</v>
       </c>
       <c r="B468">
-        <v>11368.868350000001</v>
+        <v>11344.70217</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469">
-        <v>2497.5366220000001</v>
+        <v>2559.9486139999999</v>
       </c>
       <c r="B469">
-        <v>11383.29351</v>
+        <v>11355.544169999999</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470">
-        <v>2509.3744999999999</v>
+        <v>2483.1114680000001</v>
       </c>
       <c r="B470">
-        <v>11395.131380000001</v>
+        <v>11368.868350000001</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471">
-        <v>2520.3870499999998</v>
+        <v>2497.5366220000001</v>
       </c>
       <c r="B471">
-        <v>11406.14394</v>
+        <v>11383.29351</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472">
-        <v>2527.1247039999998</v>
+        <v>2509.3744999999999</v>
       </c>
       <c r="B472">
-        <v>11420.52303</v>
+        <v>11395.131380000001</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473">
-        <v>2539.24908</v>
+        <v>2520.3870499999998</v>
       </c>
       <c r="B473">
-        <v>11432.6474</v>
+        <v>11406.14394</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474">
-        <v>2549.9836740000001</v>
+        <v>2527.1247039999998</v>
       </c>
       <c r="B474">
-        <v>11443.382</v>
+        <v>11420.52303</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475">
-        <v>2562.2107500000002</v>
+        <v>2539.24908</v>
       </c>
       <c r="B475">
-        <v>11455.60907</v>
+        <v>11432.6474</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476">
-        <v>2575.522833</v>
+        <v>2549.9836740000001</v>
       </c>
       <c r="B476">
-        <v>11468.92116</v>
+        <v>11443.382</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477">
-        <v>2542.6314280000001</v>
+        <v>2562.2107500000002</v>
       </c>
       <c r="B477">
-        <v>11477.726259999999</v>
+        <v>11455.60907</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478">
-        <v>2555.6925219999998</v>
+        <v>2575.522833</v>
       </c>
       <c r="B478">
-        <v>11490.78736</v>
+        <v>11468.92116</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479">
-        <v>2569.1349479999999</v>
+        <v>2542.6314280000001</v>
       </c>
       <c r="B479">
-        <v>11504.22978</v>
+        <v>11477.726259999999</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480">
-        <v>2581.0028269999998</v>
+        <v>2555.6925219999998</v>
       </c>
       <c r="B480">
-        <v>11516.097659999999</v>
+        <v>11490.78736</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481">
-        <v>2594.9591839999998</v>
+        <v>2569.1349479999999</v>
       </c>
       <c r="B481">
-        <v>11530.05402</v>
+        <v>11504.22978</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482">
-        <v>2608.9067540000001</v>
+        <v>2581.0028269999998</v>
       </c>
       <c r="B482">
-        <v>11544.00159</v>
+        <v>11516.097659999999</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483">
-        <v>2495.4349739999998</v>
+        <v>2594.9591839999998</v>
       </c>
       <c r="B483">
-        <v>11557.87845</v>
+        <v>11530.05402</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484">
-        <v>2507.2498810000002</v>
+        <v>2608.9067540000001</v>
       </c>
       <c r="B484">
-        <v>11569.693359999999</v>
+        <v>11544.00159</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485">
-        <v>2519.3024209999999</v>
+        <v>2495.4349739999998</v>
       </c>
       <c r="B485">
-        <v>11581.7459</v>
+        <v>11557.87845</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486">
-        <v>2530.5830350000001</v>
+        <v>2507.2498810000002</v>
       </c>
       <c r="B486">
-        <v>11593.02651</v>
+        <v>11569.693359999999</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487">
-        <v>2544.5522700000001</v>
+        <v>2519.3024209999999</v>
       </c>
       <c r="B487">
-        <v>11606.99575</v>
+        <v>11581.7459</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488">
-        <v>2498.286333</v>
+        <v>2530.5830350000001</v>
       </c>
       <c r="B488">
-        <v>11619.78276</v>
+        <v>11593.02651</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489">
-        <v>2509.0047979999999</v>
+        <v>2544.5522700000001</v>
       </c>
       <c r="B489">
-        <v>11630.50122</v>
+        <v>11606.99575</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490">
-        <v>2519.9879409999999</v>
+        <v>2498.286333</v>
       </c>
       <c r="B490">
-        <v>11641.48437</v>
+        <v>11619.78276</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491">
-        <v>2996.7271689999998</v>
+        <v>2509.0047979999999</v>
       </c>
       <c r="B491">
-        <v>12118.223599999999</v>
+        <v>11630.50122</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492">
-        <v>3009.5330760000002</v>
+        <v>2519.9879409999999</v>
       </c>
       <c r="B492">
-        <v>12131.029500000001</v>
+        <v>11641.48437</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493">
-        <v>2977.5958660000001</v>
+        <v>2996.7271689999998</v>
       </c>
       <c r="B493">
-        <v>12142.68807</v>
+        <v>12118.223599999999</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494">
-        <v>3032.595061</v>
+        <v>3009.5330760000002</v>
       </c>
       <c r="B494">
-        <v>12154.091490000001</v>
+        <v>12131.029500000001</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495">
-        <v>3004.6806299999998</v>
+        <v>2977.5958660000001</v>
       </c>
       <c r="B495">
-        <v>12169.77283</v>
+        <v>12142.68807</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496">
-        <v>3014.2813409999999</v>
+        <v>3032.595061</v>
       </c>
       <c r="B496">
-        <v>12179.373540000001</v>
+        <v>12154.091490000001</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497">
-        <v>3024.2623010000002</v>
+        <v>3004.6806299999998</v>
       </c>
       <c r="B497">
-        <v>12189.354499999999</v>
+        <v>12169.77283</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498">
-        <v>3036.1804069999998</v>
+        <v>3014.2813409999999</v>
       </c>
       <c r="B498">
-        <v>12201.27261</v>
+        <v>12179.373540000001</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499">
-        <v>2971.3393540000002</v>
+        <v>3024.2623010000002</v>
       </c>
       <c r="B499">
-        <v>12214.066269999999</v>
+        <v>12189.354499999999</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500">
-        <v>2985.5676360000002</v>
+        <v>3036.1804069999998</v>
       </c>
       <c r="B500">
-        <v>12228.294550000001</v>
+        <v>12201.27261</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501">
-        <v>2999.6520190000001</v>
+        <v>2971.3393540000002</v>
       </c>
       <c r="B501">
-        <v>12242.378930000001</v>
+        <v>12214.066269999999</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502">
-        <v>3008.1697909999998</v>
+        <v>2985.5676360000002</v>
       </c>
       <c r="B502">
-        <v>12250.896699999999</v>
+        <v>12228.294550000001</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503">
-        <v>3022.9177030000001</v>
+        <v>2999.6520190000001</v>
       </c>
       <c r="B503">
-        <v>12265.644619999999</v>
+        <v>12242.378930000001</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504">
-        <v>3037.283398</v>
+        <v>3008.1697909999998</v>
       </c>
       <c r="B504">
-        <v>12280.01031</v>
+        <v>12250.896699999999</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505">
-        <v>2305.9189329999999</v>
+        <v>3022.9177030000001</v>
       </c>
       <c r="B505">
-        <v>12290.9756</v>
+        <v>12265.644619999999</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506">
-        <v>2320.7215230000002</v>
+        <v>3037.283398</v>
       </c>
       <c r="B506">
-        <v>12305.778190000001</v>
+        <v>12280.01031</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507">
-        <v>2331.7443360000002</v>
+        <v>2305.9189329999999</v>
       </c>
       <c r="B507">
-        <v>12316.800999999999</v>
+        <v>12290.9756</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508">
-        <v>2346.2746459999998</v>
+        <v>2320.7215230000002</v>
       </c>
       <c r="B508">
-        <v>12331.33131</v>
+        <v>12305.778190000001</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509">
-        <v>2345.2521059999999</v>
+        <v>2331.7443360000002</v>
       </c>
       <c r="B509">
-        <v>12341.8927</v>
+        <v>12316.800999999999</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510">
-        <v>2359.7598370000001</v>
+        <v>2346.2746459999998</v>
       </c>
       <c r="B510">
-        <v>12356.40043</v>
+        <v>12331.33131</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511">
-        <v>2374.6765890000001</v>
+        <v>2345.2521059999999</v>
       </c>
       <c r="B511">
-        <v>12371.31718</v>
+        <v>12341.8927</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512">
-        <v>2388.950742</v>
+        <v>2359.7598370000001</v>
       </c>
       <c r="B512">
-        <v>12385.591340000001</v>
+        <v>12356.40043</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513">
-        <v>2362.825284</v>
+        <v>2374.6765890000001</v>
       </c>
       <c r="B513">
-        <v>12400.706099999999</v>
+        <v>12371.31718</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514">
-        <v>2419.1729989999999</v>
+        <v>2388.950742</v>
       </c>
       <c r="B514">
-        <v>12415.81359</v>
+        <v>12385.591340000001</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515">
-        <v>2392.1307849999998</v>
+        <v>2362.825284</v>
       </c>
       <c r="B515">
-        <v>12430.0116</v>
+        <v>12400.706099999999</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516">
-        <v>2407.3079849999999</v>
+        <v>2419.1729989999999</v>
       </c>
       <c r="B516">
-        <v>12445.1888</v>
+        <v>12415.81359</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517">
-        <v>2415.733772</v>
+        <v>2392.1307849999998</v>
       </c>
       <c r="B517">
-        <v>12453.614579999999</v>
+        <v>12430.0116</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518">
-        <v>2429.7406550000001</v>
+        <v>2407.3079849999999</v>
       </c>
       <c r="B518">
-        <v>12467.62147</v>
+        <v>12445.1888</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519">
-        <v>2444.159678</v>
+        <v>2415.733772</v>
       </c>
       <c r="B519">
-        <v>12482.040489999999</v>
+        <v>12453.614579999999</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520">
-        <v>1693.422722</v>
+        <v>2429.7406550000001</v>
       </c>
       <c r="B520">
-        <v>12492.63617</v>
+        <v>12467.62147</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521">
-        <v>1705.949519</v>
+        <v>2444.159678</v>
       </c>
       <c r="B521">
-        <v>12505.162969999999</v>
+        <v>12482.040489999999</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522">
-        <v>1717.3392080000001</v>
+        <v>1693.422722</v>
       </c>
       <c r="B522">
-        <v>12516.552659999999</v>
+        <v>12492.63617</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523">
-        <v>1728.8591759999999</v>
+        <v>1705.949519</v>
       </c>
       <c r="B523">
-        <v>12528.072620000001</v>
+        <v>12505.162969999999</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524">
-        <v>1742.544791</v>
+        <v>1717.3392080000001</v>
       </c>
       <c r="B524">
-        <v>12541.758239999999</v>
+        <v>12516.552659999999</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525">
-        <v>1663.5185939999999</v>
+        <v>1728.8591759999999</v>
       </c>
       <c r="B525">
-        <v>12553.58128</v>
+        <v>12528.072620000001</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526">
-        <v>1674.7242920000001</v>
+        <v>1742.544791</v>
       </c>
       <c r="B526">
-        <v>12564.786980000001</v>
+        <v>12541.758239999999</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527">
-        <v>1688.5113349999999</v>
+        <v>1663.5185939999999</v>
       </c>
       <c r="B527">
-        <v>12578.57402</v>
+        <v>12553.58128</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528">
-        <v>1703.0170089999999</v>
+        <v>1674.7242920000001</v>
       </c>
       <c r="B528">
-        <v>12593.0797</v>
+        <v>12564.786980000001</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529">
-        <v>1718.461384</v>
+        <v>1688.5113349999999</v>
       </c>
       <c r="B529">
-        <v>12608.524069999999</v>
+        <v>12578.57402</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530">
-        <v>1647.797671</v>
+        <v>1703.0170089999999</v>
       </c>
       <c r="B530">
-        <v>12620.199070000001</v>
+        <v>12593.0797</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531">
-        <v>1659.969474</v>
+        <v>1718.461384</v>
       </c>
       <c r="B531">
-        <v>12632.370870000001</v>
+        <v>12608.524069999999</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532">
-        <v>1671.8558840000001</v>
+        <v>1647.797671</v>
       </c>
       <c r="B532">
-        <v>12644.25728</v>
+        <v>12620.199070000001</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533">
-        <v>1683.881721</v>
+        <v>1659.969474</v>
       </c>
       <c r="B533">
-        <v>12656.28312</v>
+        <v>12632.370870000001</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534">
-        <v>1620.5062109999999</v>
+        <v>1671.8558840000001</v>
       </c>
       <c r="B534">
-        <v>12669.986290000001</v>
+        <v>12644.25728</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535">
-        <v>1709.470589</v>
+        <v>1683.881721</v>
       </c>
       <c r="B535">
-        <v>12681.87199</v>
+        <v>12656.28312</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536">
-        <v>1645.2581889999999</v>
+        <v>1620.5062109999999</v>
       </c>
       <c r="B536">
-        <v>12694.73826</v>
+        <v>12669.986290000001</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537">
-        <v>1655.961231</v>
+        <v>1709.470589</v>
       </c>
       <c r="B537">
-        <v>12705.4413</v>
+        <v>12681.87199</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538">
-        <v>1668.8213880000001</v>
+        <v>1645.2581889999999</v>
       </c>
       <c r="B538">
-        <v>12718.301460000001</v>
+        <v>12694.73826</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539">
-        <v>1610.393693</v>
+        <v>1655.961231</v>
       </c>
       <c r="B539">
-        <v>12732.39975</v>
+        <v>12705.4413</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540">
-        <v>1693.3098239999999</v>
+        <v>1668.8213880000001</v>
       </c>
       <c r="B540">
-        <v>12742.7899</v>
+        <v>12718.301460000001</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541">
-        <v>1635.465696</v>
+        <v>1610.393693</v>
       </c>
       <c r="B541">
-        <v>12757.471750000001</v>
+        <v>12732.39975</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542">
-        <v>1645.438584</v>
+        <v>1693.3098239999999</v>
       </c>
       <c r="B542">
-        <v>12767.44464</v>
+        <v>12742.7899</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543">
-        <v>1657.700574</v>
+        <v>1635.465696</v>
       </c>
       <c r="B543">
-        <v>12779.706630000001</v>
+        <v>12757.471750000001</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544">
-        <v>1670.1408100000001</v>
+        <v>1645.438584</v>
       </c>
       <c r="B544">
-        <v>12792.146860000001</v>
+        <v>12767.44464</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545">
-        <v>1683.3047839999999</v>
+        <v>1657.700574</v>
       </c>
       <c r="B545">
-        <v>12805.31084</v>
+        <v>12779.706630000001</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546">
-        <v>1656.7900139999999</v>
+        <v>1670.1408100000001</v>
       </c>
       <c r="B546">
-        <v>12819.19536</v>
+        <v>12792.146860000001</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547">
-        <v>1710.722489</v>
+        <v>1683.3047839999999</v>
       </c>
       <c r="B547">
-        <v>12832.72854</v>
+        <v>12805.31084</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548">
-        <v>1682.0968989999999</v>
+        <v>1656.7900139999999</v>
       </c>
       <c r="B548">
-        <v>12844.50224</v>
+        <v>12819.19536</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549">
-        <v>1694.6334649999999</v>
+        <v>1710.722489</v>
       </c>
       <c r="B549">
-        <v>12857.03881</v>
+        <v>12832.72854</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550">
-        <v>1708.8449760000001</v>
+        <v>1682.0968989999999</v>
       </c>
       <c r="B550">
-        <v>12871.250319999999</v>
+        <v>12844.50224</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551">
-        <v>2236.8364539999998</v>
+        <v>1694.6334649999999</v>
       </c>
       <c r="B551">
-        <v>13399.2418</v>
+        <v>12857.03881</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552">
-        <v>2208.8702549999998</v>
+        <v>1708.8449760000001</v>
       </c>
       <c r="B552">
-        <v>13408.441650000001</v>
+        <v>12871.250319999999</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553">
-        <v>2234.5784269999999</v>
+        <v>2236.8364539999998</v>
       </c>
       <c r="B553">
-        <v>13434.149820000001</v>
+        <v>13399.2418</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554">
-        <v>2244.621545</v>
+        <v>2208.8702549999998</v>
       </c>
       <c r="B554">
-        <v>13444.192940000001</v>
+        <v>13408.441650000001</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555">
-        <v>2258.6281869999998</v>
+        <v>2234.5784269999999</v>
       </c>
       <c r="B555">
-        <v>13458.19958</v>
+        <v>13434.149820000001</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556">
-        <v>2273.2421509999999</v>
+        <v>2244.621545</v>
       </c>
       <c r="B556">
-        <v>13472.813550000001</v>
+        <v>13444.192940000001</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557">
-        <v>2285.2559529999999</v>
+        <v>2258.6281869999998</v>
       </c>
       <c r="B557">
-        <v>13484.82735</v>
+        <v>13458.19958</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558">
-        <v>2224.2741390000001</v>
+        <v>2273.2421509999999</v>
       </c>
       <c r="B558">
-        <v>13499.484329999999</v>
+        <v>13472.813550000001</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559">
-        <v>2235.860831</v>
+        <v>2285.2559529999999</v>
       </c>
       <c r="B559">
-        <v>13511.071019999999</v>
+        <v>13484.82735</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560">
-        <v>2202.5392529999999</v>
+        <v>2224.2741390000001</v>
       </c>
       <c r="B560">
-        <v>13525.374110000001</v>
+        <v>13499.484329999999</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561">
-        <v>2216.5344409999998</v>
+        <v>2235.860831</v>
       </c>
       <c r="B561">
-        <v>13539.3693</v>
+        <v>13511.071019999999</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562">
-        <v>2226.9428750000002</v>
+        <v>2202.5392529999999</v>
       </c>
       <c r="B562">
-        <v>13549.77774</v>
+        <v>13525.374110000001</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563">
-        <v>2238.720096</v>
+        <v>2216.5344409999998</v>
       </c>
       <c r="B563">
-        <v>13561.554959999999</v>
+        <v>13539.3693</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564">
-        <v>2251.0201430000002</v>
+        <v>2226.9428750000002</v>
       </c>
       <c r="B564">
-        <v>13573.855009999999</v>
+        <v>13549.77774</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565">
-        <v>2262.353063</v>
+        <v>2238.720096</v>
       </c>
       <c r="B565">
-        <v>13585.18792</v>
+        <v>13561.554959999999</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566">
-        <v>2230.6630449999998</v>
+        <v>2251.0201430000002</v>
       </c>
       <c r="B566">
-        <v>13598.66563</v>
+        <v>13573.855009999999</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567">
-        <v>2242.5348399999998</v>
+        <v>2262.353063</v>
       </c>
       <c r="B567">
-        <v>13610.53743</v>
+        <v>13585.18792</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568">
-        <v>2252.9321890000001</v>
+        <v>2230.6630449999998</v>
       </c>
       <c r="B568">
-        <v>13620.93477</v>
+        <v>13598.66563</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569">
-        <v>2218.2783909999998</v>
+        <v>2242.5348399999998</v>
       </c>
       <c r="B569">
-        <v>13631.63571</v>
+        <v>13610.53743</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570">
-        <v>2229.5899209999998</v>
+        <v>2252.9321890000001</v>
       </c>
       <c r="B570">
-        <v>13642.94724</v>
+        <v>13620.93477</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571">
-        <v>2285.4962869999999</v>
+        <v>2218.2783909999998</v>
       </c>
       <c r="B571">
-        <v>13653.498869999999</v>
+        <v>13631.63571</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572">
-        <v>2251.8582940000001</v>
+        <v>2229.5899209999998</v>
       </c>
       <c r="B572">
-        <v>13665.215609999999</v>
+        <v>13642.94724</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573">
-        <v>2192.7838350000002</v>
+        <v>2285.4962869999999</v>
       </c>
       <c r="B573">
-        <v>13677.267330000001</v>
+        <v>13653.498869999999</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574">
-        <v>2276.2427600000001</v>
+        <v>2251.8582940000001</v>
       </c>
       <c r="B574">
-        <v>13689.60008</v>
+        <v>13665.215609999999</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575">
-        <v>2217.1005289999998</v>
+        <v>2192.7838350000002</v>
       </c>
       <c r="B575">
-        <v>13701.58402</v>
+        <v>13677.267330000001</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576">
-        <v>2231.177064</v>
+        <v>2276.2427600000001</v>
       </c>
       <c r="B576">
-        <v>13715.660550000001</v>
+        <v>13689.60008</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577">
-        <v>2242.7073009999999</v>
+        <v>2217.1005289999998</v>
       </c>
       <c r="B577">
-        <v>13727.190790000001</v>
+        <v>13701.58402</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578">
-        <v>2177.211037</v>
+        <v>2231.177064</v>
       </c>
       <c r="B578">
-        <v>13739.890100000001</v>
+        <v>13715.660550000001</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579">
-        <v>2269.0547769999998</v>
+        <v>2242.7073009999999</v>
       </c>
       <c r="B579">
-        <v>13753.538269999999</v>
+        <v>13727.190790000001</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580">
-        <v>2202.709398</v>
+        <v>2177.211037</v>
       </c>
       <c r="B580">
-        <v>13765.38846</v>
+        <v>13739.890100000001</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581">
-        <v>2217.6921910000001</v>
+        <v>2269.0547769999998</v>
       </c>
       <c r="B581">
-        <v>13780.37125</v>
+        <v>13753.538269999999</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582">
-        <v>2232.0698269999998</v>
+        <v>2202.709398</v>
       </c>
       <c r="B582">
-        <v>13794.748890000001</v>
+        <v>13765.38846</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583">
-        <v>2189.0283290000002</v>
+        <v>2217.6921910000001</v>
       </c>
       <c r="B583">
-        <v>13805.218849999999</v>
+        <v>13780.37125</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584">
-        <v>2333.8778820000002</v>
+        <v>2232.0698269999998</v>
       </c>
       <c r="B584">
-        <v>13818.361370000001</v>
+        <v>13794.748890000001</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585">
-        <v>2269.935187</v>
+        <v>2189.0283290000002</v>
       </c>
       <c r="B585">
-        <v>13832.614250000001</v>
+        <v>13805.218849999999</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586">
-        <v>2229.7667499999998</v>
+        <v>2333.8778820000002</v>
       </c>
       <c r="B586">
-        <v>13845.957270000001</v>
+        <v>13818.361370000001</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587">
-        <v>2241.1504329999998</v>
+        <v>2269.935187</v>
       </c>
       <c r="B587">
-        <v>13857.34095</v>
+        <v>13832.614250000001</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588">
-        <v>2254.1224350000002</v>
+        <v>2229.7667499999998</v>
       </c>
       <c r="B588">
-        <v>13870.31295</v>
+        <v>13845.957270000001</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589">
-        <v>2268.4227209999999</v>
+        <v>2241.1504329999998</v>
       </c>
       <c r="B589">
-        <v>13884.613240000001</v>
+        <v>13857.34095</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590">
-        <v>1734.849101</v>
+        <v>2254.1224350000002</v>
       </c>
       <c r="B590">
-        <v>13896.836370000001</v>
+        <v>13870.31295</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591">
-        <v>1748.361915</v>
+        <v>2268.4227209999999</v>
       </c>
       <c r="B591">
-        <v>13910.349179999999</v>
+        <v>13884.613240000001</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592">
-        <v>1761.0100689999999</v>
+        <v>1734.849101</v>
       </c>
       <c r="B592">
-        <v>13922.99734</v>
+        <v>13896.836370000001</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593">
-        <v>2318.910007</v>
+        <v>1748.361915</v>
       </c>
       <c r="B593">
-        <v>13935.10053</v>
+        <v>13910.349179999999</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594">
-        <v>1786.1896280000001</v>
+        <v>1761.0100689999999</v>
       </c>
       <c r="B594">
-        <v>13948.1769</v>
+        <v>13922.99734</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595">
-        <v>1796.8795170000001</v>
+        <v>2318.910007</v>
       </c>
       <c r="B595">
-        <v>13958.86679</v>
+        <v>13935.10053</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596">
-        <v>1751.668208</v>
+        <v>1786.1896280000001</v>
       </c>
       <c r="B596">
-        <v>13970.194219999999</v>
+        <v>13948.1769</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597">
-        <v>1766.4224939999999</v>
+        <v>1796.8795170000001</v>
       </c>
       <c r="B597">
-        <v>13984.94851</v>
+        <v>13958.86679</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598">
-        <v>1781.8330249999999</v>
+        <v>1751.668208</v>
       </c>
       <c r="B598">
-        <v>14000.359039999999</v>
+        <v>13970.194219999999</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599">
-        <v>1853.2511919999999</v>
+        <v>1766.4224939999999</v>
       </c>
       <c r="B599">
-        <v>14015.23846</v>
+        <v>13984.94851</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600">
-        <v>1810.5849189999999</v>
+        <v>1781.8330249999999</v>
       </c>
       <c r="B600">
-        <v>14029.110930000001</v>
+        <v>14000.359039999999</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601">
-        <v>2315.1158340000002</v>
+        <v>1853.2511919999999</v>
       </c>
       <c r="B601">
-        <v>14610.610119999999</v>
+        <v>14015.23846</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602">
-        <v>2324.4726959999998</v>
+        <v>1810.5849189999999</v>
       </c>
       <c r="B602">
-        <v>14619.966979999999</v>
+        <v>14029.110930000001</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603">
-        <v>2342.578297</v>
+        <v>2315.1158340000002</v>
       </c>
       <c r="B603">
-        <v>14638.07258</v>
+        <v>14610.610119999999</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604">
-        <v>2356.6282230000002</v>
+        <v>2324.4726959999998</v>
       </c>
       <c r="B604">
-        <v>14652.122509999999</v>
+        <v>14619.966979999999</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605">
-        <v>2370.923847</v>
+        <v>2342.578297</v>
       </c>
       <c r="B605">
-        <v>14666.41813</v>
+        <v>14638.07258</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606">
-        <v>2382.816186</v>
+        <v>2356.6282230000002</v>
       </c>
       <c r="B606">
-        <v>14678.31047</v>
+        <v>14652.122509999999</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607">
-        <v>2355.551782</v>
+        <v>2370.923847</v>
       </c>
       <c r="B607">
-        <v>14692.44398</v>
+        <v>14666.41813</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608">
-        <v>2369.581682</v>
+        <v>2382.816186</v>
       </c>
       <c r="B608">
-        <v>14706.47388</v>
+        <v>14678.31047</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609">
-        <v>2383.730423</v>
+        <v>2355.551782</v>
       </c>
       <c r="B609">
-        <v>14720.62262</v>
+        <v>14692.44398</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610">
-        <v>2397.3327730000001</v>
+        <v>2369.581682</v>
       </c>
       <c r="B610">
-        <v>14734.224969999999</v>
+        <v>14706.47388</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611">
-        <v>2323.2788820000001</v>
+        <v>2383.730423</v>
       </c>
       <c r="B611">
-        <v>14747.983130000001</v>
+        <v>14720.62262</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612">
-        <v>2338.2662319999999</v>
+        <v>2397.3327730000001</v>
       </c>
       <c r="B612">
-        <v>14762.97048</v>
+        <v>14734.224969999999</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613">
-        <v>2351.6655839999999</v>
+        <v>2323.2788820000001</v>
       </c>
       <c r="B613">
-        <v>14776.369839999999</v>
+        <v>14747.983130000001</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614">
-        <v>2362.369107</v>
+        <v>2338.2662319999999</v>
       </c>
       <c r="B614">
-        <v>14787.07336</v>
+        <v>14762.97048</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615">
-        <v>2376.8802190000001</v>
+        <v>2351.6655839999999</v>
       </c>
       <c r="B615">
-        <v>14801.58447</v>
+        <v>14776.369839999999</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616">
-        <v>2391.1413600000001</v>
+        <v>2362.369107</v>
       </c>
       <c r="B616">
-        <v>14815.84561</v>
+        <v>14787.07336</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617">
-        <v>2402.4700079999998</v>
+        <v>2376.8802190000001</v>
       </c>
       <c r="B617">
-        <v>14827.17426</v>
+        <v>14801.58447</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618">
-        <v>2345.8827919999999</v>
+        <v>2391.1413600000001</v>
       </c>
       <c r="B618">
-        <v>14838.32962</v>
+        <v>14815.84561</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619">
-        <v>2357.785089</v>
+        <v>2402.4700079999998</v>
       </c>
       <c r="B619">
-        <v>14850.23192</v>
+        <v>14827.17426</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620">
-        <v>2370.4133780000002</v>
+        <v>2345.8827919999999</v>
       </c>
       <c r="B620">
-        <v>14862.860199999999</v>
+        <v>14838.32962</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621">
-        <v>2383.1563150000002</v>
+        <v>2357.785089</v>
       </c>
       <c r="B621">
-        <v>14875.603139999999</v>
+        <v>14850.23192</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622">
-        <v>2332.8086800000001</v>
+        <v>2370.4133780000002</v>
       </c>
       <c r="B622">
-        <v>14885.856760000001</v>
+        <v>14862.860199999999</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623">
-        <v>2344.9791009999999</v>
+        <v>2383.1563150000002</v>
       </c>
       <c r="B623">
-        <v>14898.027190000001</v>
+        <v>14875.603139999999</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624">
-        <v>2357.7376370000002</v>
+        <v>2332.8086800000001</v>
       </c>
       <c r="B624">
-        <v>14910.78572</v>
+        <v>14885.856760000001</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625">
-        <v>2371.806497</v>
+        <v>2344.9791009999999</v>
       </c>
       <c r="B625">
-        <v>14924.854579999999</v>
+        <v>14898.027190000001</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626">
-        <v>2383.640007</v>
+        <v>2357.7376370000002</v>
       </c>
       <c r="B626">
-        <v>14936.68809</v>
+        <v>14910.78572</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627">
-        <v>2326.03125</v>
+        <v>2371.806497</v>
       </c>
       <c r="B627">
-        <v>14947.64178</v>
+        <v>14924.854579999999</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628">
-        <v>2334.9948209999998</v>
+        <v>2383.640007</v>
       </c>
       <c r="B628">
-        <v>14956.60535</v>
+        <v>14936.68809</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629">
-        <v>2348.2213369999999</v>
+        <v>2326.03125</v>
       </c>
       <c r="B629">
-        <v>14969.83187</v>
+        <v>14947.64178</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630">
-        <v>2361.9993100000002</v>
+        <v>2334.9948209999998</v>
       </c>
       <c r="B630">
-        <v>14983.609839999999</v>
+        <v>14956.60535</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631">
-        <v>3058.5868500000001</v>
+        <v>2348.2213369999999</v>
       </c>
       <c r="B631">
-        <v>15680.19738</v>
+        <v>14969.83187</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632">
-        <v>3074.4518739999999</v>
+        <v>2361.9993100000002</v>
       </c>
       <c r="B632">
-        <v>15696.06241</v>
+        <v>14983.609839999999</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633">
-        <v>3016.4617119999998</v>
+        <v>3058.5868500000001</v>
       </c>
       <c r="B633">
-        <v>15708.35476</v>
+        <v>15680.19738</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634">
-        <v>3028.6518209999999</v>
+        <v>3074.4518739999999</v>
       </c>
       <c r="B634">
-        <v>15720.54487</v>
+        <v>15696.06241</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635">
-        <v>3042.4343509999999</v>
+        <v>3016.4617119999998</v>
       </c>
       <c r="B635">
-        <v>15734.3274</v>
+        <v>15708.35476</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636">
-        <v>3054.7428110000001</v>
+        <v>3028.6518209999999</v>
       </c>
       <c r="B636">
-        <v>15746.63586</v>
+        <v>15720.54487</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637">
-        <v>3069.5855390000002</v>
+        <v>3042.4343509999999</v>
       </c>
       <c r="B637">
-        <v>15761.478590000001</v>
+        <v>15734.3274</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638">
-        <v>3020.7570639999999</v>
+        <v>3054.7428110000001</v>
       </c>
       <c r="B638">
-        <v>15775.306479999999</v>
+        <v>15746.63586</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639">
-        <v>2949.2877319999998</v>
+        <v>3069.5855390000002</v>
       </c>
       <c r="B639">
-        <v>15787.53643</v>
+        <v>15761.478590000001</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640">
-        <v>3045.6311260000002</v>
+        <v>3020.7570639999999</v>
       </c>
       <c r="B640">
-        <v>15800.180539999999</v>
+        <v>15775.306479999999</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641">
-        <v>3060.201223</v>
+        <v>2949.2877319999998</v>
       </c>
       <c r="B641">
-        <v>15814.75064</v>
+        <v>15787.53643</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642">
-        <v>2991.0521520000002</v>
+        <v>3045.6311260000002</v>
       </c>
       <c r="B642">
-        <v>15829.30085</v>
+        <v>15800.180539999999</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643">
-        <v>3089.6216629999999</v>
+        <v>3060.201223</v>
       </c>
       <c r="B643">
-        <v>15844.17108</v>
+        <v>15814.75064</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644">
-        <v>3015.7918279999999</v>
+        <v>2991.0521520000002</v>
       </c>
       <c r="B644">
-        <v>15854.04052</v>
+        <v>15829.30085</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645">
-        <v>3023.7590129999999</v>
+        <v>3089.6216629999999</v>
       </c>
       <c r="B645">
-        <v>15865.799139999999</v>
+        <v>15844.17108</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646">
-        <v>3038.3326619999998</v>
+        <v>3015.7918279999999</v>
       </c>
       <c r="B646">
-        <v>15880.372789999999</v>
+        <v>15854.04052</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647">
-        <v>3053.658852</v>
+        <v>3023.7590129999999</v>
       </c>
       <c r="B647">
-        <v>15891.90755</v>
+        <v>15865.799139999999</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648">
-        <v>3063.3276489999998</v>
+        <v>3038.3326619999998</v>
       </c>
       <c r="B648">
-        <v>15905.36778</v>
+        <v>15880.372789999999</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649">
-        <v>2509.9059849999999</v>
+        <v>3053.658852</v>
       </c>
       <c r="B649">
-        <v>15918.46031</v>
+        <v>15891.90755</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650">
-        <v>3091.5064560000001</v>
+        <v>3063.3276489999998</v>
       </c>
       <c r="B650">
-        <v>15933.54659</v>
+        <v>15905.36778</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651">
-        <v>2537.7770169999999</v>
+        <v>2509.9059849999999</v>
       </c>
       <c r="B651">
-        <v>15946.331340000001</v>
+        <v>15918.46031</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652">
-        <v>2553.4770530000001</v>
+        <v>3091.5064560000001</v>
       </c>
       <c r="B652">
-        <v>15962.03138</v>
+        <v>15933.54659</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653">
-        <v>2565.0212200000001</v>
+        <v>2537.7770169999999</v>
       </c>
       <c r="B653">
-        <v>15973.57555</v>
+        <v>15946.331340000001</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654">
-        <v>2495.1365110000002</v>
+        <v>2553.4770530000001</v>
       </c>
       <c r="B654">
-        <v>15988.06285</v>
+        <v>15962.03138</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655">
-        <v>2508.7881040000002</v>
+        <v>2565.0212200000001</v>
       </c>
       <c r="B655">
-        <v>16001.714449999999</v>
+        <v>15973.57555</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656">
-        <v>2523.0405209999999</v>
+        <v>2495.1365110000002</v>
       </c>
       <c r="B656">
-        <v>16015.96686</v>
+        <v>15988.06285</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657">
-        <v>2538.712274</v>
+        <v>2508.7881040000002</v>
       </c>
       <c r="B657">
-        <v>16031.63862</v>
+        <v>16001.714449999999</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658">
-        <v>2550.4017880000001</v>
+        <v>2523.0405209999999</v>
       </c>
       <c r="B658">
-        <v>16043.32813</v>
+        <v>16015.96686</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659">
-        <v>2453.5249600000002</v>
+        <v>2538.712274</v>
       </c>
       <c r="B659">
-        <v>16052.70645</v>
+        <v>16031.63862</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660">
-        <v>2574.353044</v>
+        <v>2550.4017880000001</v>
       </c>
       <c r="B660">
-        <v>16067.27939</v>
+        <v>16043.32813</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661">
-        <v>2479.2876259999998</v>
+        <v>2453.5249600000002</v>
       </c>
       <c r="B661">
-        <v>16078.46912</v>
+        <v>16052.70645</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662">
-        <v>2492.487568</v>
+        <v>2574.353044</v>
       </c>
       <c r="B662">
-        <v>16091.66906</v>
+        <v>16067.27939</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663">
-        <v>2506.621764</v>
+        <v>2479.2876259999998</v>
       </c>
       <c r="B663">
-        <v>16105.803250000001</v>
+        <v>16078.46912</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664">
-        <v>2516.828595</v>
+        <v>2492.487568</v>
       </c>
       <c r="B664">
-        <v>16118.036980000001</v>
+        <v>16091.66906</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665">
-        <v>2532.1969829999998</v>
+        <v>2506.621764</v>
       </c>
       <c r="B665">
-        <v>16133.40537</v>
+        <v>16105.803250000001</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666">
-        <v>2544.0692060000001</v>
+        <v>2516.828595</v>
       </c>
       <c r="B666">
-        <v>16145.27759</v>
+        <v>16118.036980000001</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667">
-        <v>2556.307264</v>
+        <v>2532.1969829999998</v>
       </c>
       <c r="B667">
-        <v>16157.515649999999</v>
+        <v>16133.40537</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668">
-        <v>2499.3607050000001</v>
+        <v>2544.0692060000001</v>
       </c>
       <c r="B668">
-        <v>16170.20556</v>
+        <v>16145.27759</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669">
-        <v>2512.2438240000001</v>
+        <v>2556.307264</v>
       </c>
       <c r="B669">
-        <v>16183.088680000001</v>
+        <v>16157.515649999999</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670">
-        <v>2526.2358490000001</v>
+        <v>2499.3607050000001</v>
       </c>
       <c r="B670">
-        <v>16197.08071</v>
+        <v>16170.20556</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671">
-        <v>2538.5195840000001</v>
+        <v>2512.2438240000001</v>
       </c>
       <c r="B671">
-        <v>16209.364439999999</v>
+        <v>16183.088680000001</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672">
-        <v>2548.9221539999999</v>
+        <v>2526.2358490000001</v>
       </c>
       <c r="B672">
-        <v>16219.76701</v>
+        <v>16197.08071</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673">
-        <v>2560.5397520000001</v>
+        <v>2538.5195840000001</v>
       </c>
       <c r="B673">
-        <v>16231.384609999999</v>
+        <v>16209.364439999999</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674">
-        <v>2419.8186900000001</v>
+        <v>2548.9221539999999</v>
       </c>
       <c r="B674">
-        <v>16245.377570000001</v>
+        <v>16219.76701</v>
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675">
-        <v>2434.9033300000001</v>
+        <v>2560.5397520000001</v>
       </c>
       <c r="B675">
-        <v>16260.46221</v>
+        <v>16231.384609999999</v>
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676">
-        <v>2448.1227760000002</v>
+        <v>2419.8186900000001</v>
       </c>
       <c r="B676">
-        <v>16273.68165</v>
+        <v>16245.377570000001</v>
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677">
-        <v>2455.9620920000002</v>
+        <v>2434.9033300000001</v>
       </c>
       <c r="B677">
-        <v>16287.09866</v>
+        <v>16260.46221</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678">
-        <v>2476.6256990000002</v>
+        <v>2448.1227760000002</v>
       </c>
       <c r="B678">
-        <v>16302.184579999999</v>
+        <v>16273.68165</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679">
-        <v>2483.7031189999998</v>
+        <v>2455.9620920000002</v>
       </c>
       <c r="B679">
-        <v>16314.839690000001</v>
+        <v>16287.09866</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680">
-        <v>2496.5790270000002</v>
+        <v>2476.6256990000002</v>
       </c>
       <c r="B680">
-        <v>16327.71559</v>
+        <v>16302.184579999999</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681">
-        <v>2510.3038609999999</v>
+        <v>2483.7031189999998</v>
       </c>
       <c r="B681">
-        <v>16341.440430000001</v>
+        <v>16314.839690000001</v>
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682">
-        <v>2522.7771889999999</v>
+        <v>2496.5790270000002</v>
       </c>
       <c r="B682">
-        <v>16353.91375</v>
+        <v>16327.71559</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683">
-        <v>2513.2666490000001</v>
+        <v>2510.3038609999999</v>
       </c>
       <c r="B683">
-        <v>16364.07611</v>
+        <v>16341.440430000001</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684">
-        <v>2528.232305</v>
+        <v>2522.7771889999999</v>
       </c>
       <c r="B684">
-        <v>16379.04176</v>
+        <v>16353.91375</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685">
-        <v>2540.8412960000001</v>
+        <v>2513.2666490000001</v>
       </c>
       <c r="B685">
-        <v>16391.650750000001</v>
+        <v>16364.07611</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686">
-        <v>2554.7208099999998</v>
+        <v>2528.232305</v>
       </c>
       <c r="B686">
-        <v>16405.530269999999</v>
+        <v>16379.04176</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687">
-        <v>2567.0633520000001</v>
+        <v>2540.8412960000001</v>
       </c>
       <c r="B687">
-        <v>16417.872810000001</v>
+        <v>16391.650750000001</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688">
-        <v>2481.013211</v>
+        <v>2554.7208099999998</v>
       </c>
       <c r="B688">
-        <v>16431.192510000001</v>
+        <v>16405.530269999999</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689">
-        <v>2490.4227449999998</v>
+        <v>2567.0633520000001</v>
       </c>
       <c r="B689">
-        <v>16440.602050000001</v>
+        <v>16417.872810000001</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690">
-        <v>2502.8162499999999</v>
+        <v>2481.013211</v>
       </c>
       <c r="B690">
-        <v>16452.99555</v>
+        <v>16431.192510000001</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691">
-        <v>2516.873568</v>
+        <v>2490.4227449999998</v>
       </c>
       <c r="B691">
-        <v>16467.05287</v>
+        <v>16440.602050000001</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692">
-        <v>2531.4059000000002</v>
+        <v>2502.8162499999999</v>
       </c>
       <c r="B692">
-        <v>16481.585200000001</v>
+        <v>16452.99555</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693">
-        <v>2544.680245</v>
+        <v>2516.873568</v>
       </c>
       <c r="B693">
-        <v>16494.859550000001</v>
+        <v>16467.05287</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694">
-        <v>2555.7499050000001</v>
+        <v>2531.4059000000002</v>
       </c>
       <c r="B694">
-        <v>16505.929209999998</v>
+        <v>16481.585200000001</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695">
-        <v>2495.0113120000001</v>
+        <v>2544.680245</v>
       </c>
       <c r="B695">
-        <v>16520.095010000001</v>
+        <v>16494.859550000001</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696">
-        <v>2510.189112</v>
+        <v>2555.7499050000001</v>
       </c>
       <c r="B696">
-        <v>16535.272809999999</v>
+        <v>16505.929209999998</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697">
-        <v>2522.0793309999999</v>
+        <v>2495.0113120000001</v>
       </c>
       <c r="B697">
-        <v>16547.16302</v>
+        <v>16520.095010000001</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698">
-        <v>2535.0023999999999</v>
+        <v>2510.189112</v>
       </c>
       <c r="B698">
-        <v>16560.086090000001</v>
+        <v>16535.272809999999</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699">
-        <v>2549.1536179999998</v>
+        <v>2522.0793309999999</v>
       </c>
       <c r="B699">
-        <v>16574.23731</v>
+        <v>16547.16302</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700">
-        <v>2563.0618020000002</v>
+        <v>2535.0023999999999</v>
       </c>
       <c r="B700">
-        <v>16588.145499999999</v>
+        <v>16560.086090000001</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701">
-        <v>2356.3735980000001</v>
+        <v>2549.1536179999998</v>
       </c>
       <c r="B701">
-        <v>17044.875220000002</v>
+        <v>16574.23731</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702">
-        <v>2371.4444010000002</v>
+        <v>2563.0618020000002</v>
       </c>
       <c r="B702">
-        <v>17059.946019999999</v>
+        <v>16588.145499999999</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703">
-        <v>2376.411572</v>
+        <v>2356.3735980000001</v>
       </c>
       <c r="B703">
-        <v>17073.872220000001</v>
+        <v>17044.875220000002</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704">
-        <v>2396.828336</v>
+        <v>2371.4444010000002</v>
       </c>
       <c r="B704">
-        <v>17085.329959999999</v>
+        <v>17059.946019999999</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705">
-        <v>2401.895552</v>
+        <v>2376.411572</v>
       </c>
       <c r="B705">
-        <v>17099.356199999998</v>
+        <v>17073.872220000001</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706">
-        <v>2410.7371819999998</v>
+        <v>2396.828336</v>
       </c>
       <c r="B706">
-        <v>17108.197830000001</v>
+        <v>17085.329959999999</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707">
-        <v>2424.77027</v>
+        <v>2401.895552</v>
       </c>
       <c r="B707">
-        <v>17122.230920000002</v>
+        <v>17099.356199999998</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708">
-        <v>2388.2830760000002</v>
+        <v>2410.7371819999998</v>
       </c>
       <c r="B708">
-        <v>17133.49008</v>
+        <v>17108.197830000001</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709">
-        <v>2403.2962440000001</v>
+        <v>2424.77027</v>
       </c>
       <c r="B709">
-        <v>17148.503250000002</v>
+        <v>17122.230920000002</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710">
-        <v>2414.0305440000002</v>
+        <v>2388.2830760000002</v>
       </c>
       <c r="B710">
-        <v>17159.237550000002</v>
+        <v>17133.49008</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711">
-        <v>2427.8409670000001</v>
+        <v>2403.2962440000001</v>
       </c>
       <c r="B711">
-        <v>17173.04797</v>
+        <v>17148.503250000002</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712">
-        <v>2349.4787510000001</v>
+        <v>2414.0305440000002</v>
       </c>
       <c r="B712">
-        <v>17186.636699999999</v>
+        <v>17159.237550000002</v>
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713">
-        <v>2359.8701139999998</v>
+        <v>2427.8409670000001</v>
       </c>
       <c r="B713">
-        <v>17197.02807</v>
+        <v>17173.04797</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714">
-        <v>2374.0533399999999</v>
+        <v>2349.4787510000001</v>
       </c>
       <c r="B714">
-        <v>17211.211289999999</v>
+        <v>17186.636699999999</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715">
-        <v>2386.695757</v>
+        <v>2359.8701139999998</v>
       </c>
       <c r="B715">
-        <v>17223.853709999999</v>
+        <v>17197.02807</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716">
-        <v>2399.542884</v>
+        <v>2374.0533399999999</v>
       </c>
       <c r="B716">
-        <v>17236.700840000001</v>
+        <v>17211.211289999999</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717">
-        <v>2407.8197479999999</v>
+        <v>2386.695757</v>
       </c>
       <c r="B717">
-        <v>17249.70117</v>
+        <v>17223.853709999999</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718">
-        <v>2418.2058510000002</v>
+        <v>2399.542884</v>
       </c>
       <c r="B718">
-        <v>17260.08728</v>
+        <v>17236.700840000001</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719">
-        <v>2427.5158719999999</v>
+        <v>2407.8197479999999</v>
       </c>
       <c r="B719">
-        <v>17269.397300000001</v>
+        <v>17249.70117</v>
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720">
-        <v>2438.1405949999998</v>
+        <v>2418.2058510000002</v>
       </c>
       <c r="B720">
-        <v>17280.02202</v>
+        <v>17260.08728</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721">
-        <v>2414.8195679999999</v>
+        <v>2427.5158719999999</v>
       </c>
       <c r="B721">
-        <v>17295.030190000001</v>
+        <v>17269.397300000001</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722">
-        <v>2428.5028889999999</v>
+        <v>2438.1405949999998</v>
       </c>
       <c r="B722">
-        <v>17308.713510000001</v>
+        <v>17280.02202</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723">
-        <v>2442.6522009999999</v>
+        <v>2414.8195679999999</v>
       </c>
       <c r="B723">
-        <v>17322.862819999998</v>
+        <v>17295.030190000001</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724">
-        <v>2451.7479830000002</v>
+        <v>2428.5028889999999</v>
       </c>
       <c r="B724">
-        <v>17331.958600000002</v>
+        <v>17308.713510000001</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725">
-        <v>2396.1317300000001</v>
+        <v>2442.6522009999999</v>
       </c>
       <c r="B725">
-        <v>17342.941869999999</v>
+        <v>17322.862819999998</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726">
-        <v>2405.4685810000001</v>
+        <v>2451.7479830000002</v>
       </c>
       <c r="B726">
-        <v>17352.278719999998</v>
+        <v>17331.958600000002</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727">
-        <v>2420.3352960000002</v>
+        <v>2396.1317300000001</v>
       </c>
       <c r="B727">
-        <v>17367.14543</v>
+        <v>17342.941869999999</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728">
-        <v>2433.5685360000002</v>
+        <v>2405.4685810000001</v>
       </c>
       <c r="B728">
-        <v>17380.378669999998</v>
+        <v>17352.278719999998</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729">
-        <v>2448.1437850000002</v>
+        <v>2420.3352960000002</v>
       </c>
       <c r="B729">
-        <v>17394.95392</v>
+        <v>17367.14543</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730">
-        <v>2458.9286029999998</v>
+        <v>2433.5685360000002</v>
       </c>
       <c r="B730">
-        <v>17405.738740000001</v>
+        <v>17380.378669999998</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731">
-        <v>1715.8802720000001</v>
+        <v>2448.1437850000002</v>
       </c>
       <c r="B731">
-        <v>17418.11433</v>
+        <v>17394.95392</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732">
-        <v>1728.2465549999999</v>
+        <v>2458.9286029999998</v>
       </c>
       <c r="B732">
-        <v>17430.480619999998</v>
+        <v>17405.738740000001</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733">
-        <v>1742.8524279999999</v>
+        <v>1715.8802720000001</v>
       </c>
       <c r="B733">
-        <v>17445.086490000002</v>
+        <v>17418.11433</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734">
-        <v>1753.4350750000001</v>
+        <v>1728.2465549999999</v>
       </c>
       <c r="B734">
-        <v>17455.669140000002</v>
+        <v>17430.480619999998</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735">
-        <v>1768.902137</v>
+        <v>1742.8524279999999</v>
       </c>
       <c r="B735">
-        <v>17471.136200000001</v>
+        <v>17445.086490000002</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736">
-        <v>1702.2603059999999</v>
+        <v>1753.4350750000001</v>
       </c>
       <c r="B736">
-        <v>17484.12168</v>
+        <v>17455.669140000002</v>
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737">
-        <v>1712.54618</v>
+        <v>1768.902137</v>
       </c>
       <c r="B737">
-        <v>17494.40755</v>
+        <v>17471.136200000001</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738">
-        <v>1725.2875779999999</v>
+        <v>1702.2603059999999</v>
       </c>
       <c r="B738">
-        <v>17507.148949999999</v>
+        <v>17484.12168</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739">
-        <v>1739.198091</v>
+        <v>1712.54618</v>
       </c>
       <c r="B739">
-        <v>17521.05946</v>
+        <v>17494.40755</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740">
-        <v>1657.587307</v>
+        <v>1725.2875779999999</v>
       </c>
       <c r="B740">
-        <v>17535.21903</v>
+        <v>17507.148949999999</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741">
-        <v>1765.869455</v>
+        <v>1739.198091</v>
       </c>
       <c r="B741">
-        <v>17547.73083</v>
+        <v>17521.05946</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742">
-        <v>1680.3290320000001</v>
+        <v>1657.587307</v>
       </c>
       <c r="B742">
-        <v>17557.960760000002</v>
+        <v>17535.21903</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743">
-        <v>1692.845914</v>
+        <v>1765.869455</v>
       </c>
       <c r="B743">
-        <v>17570.477640000001</v>
+        <v>17547.73083</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744">
-        <v>1671.5457019999999</v>
+        <v>1680.3290320000001</v>
       </c>
       <c r="B744">
-        <v>17579.082910000001</v>
+        <v>17557.960760000002</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745">
-        <v>1685.8761380000001</v>
+        <v>1692.845914</v>
       </c>
       <c r="B745">
-        <v>17593.413339999999</v>
+        <v>17570.477640000001</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746">
-        <v>1700.253696</v>
+        <v>1671.5457019999999</v>
       </c>
       <c r="B746">
-        <v>17607.7909</v>
+        <v>17579.082910000001</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747">
-        <v>1670.9813859999999</v>
+        <v>1685.8761380000001</v>
       </c>
       <c r="B747">
-        <v>17621.557290000001</v>
+        <v>17593.413339999999</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748">
-        <v>1683.041604</v>
+        <v>1700.253696</v>
       </c>
       <c r="B748">
-        <v>17633.61751</v>
+        <v>17607.7909</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749">
-        <v>1694.6548769999999</v>
+        <v>1670.9813859999999</v>
       </c>
       <c r="B749">
-        <v>17645.230780000002</v>
+        <v>17621.557290000001</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750">
-        <v>1708.882321</v>
+        <v>1683.041604</v>
       </c>
       <c r="B750">
-        <v>17659.45822</v>
+        <v>17633.61751</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751">
-        <v>2269.0154459999999</v>
+        <v>1694.6548769999999</v>
       </c>
       <c r="B751">
-        <v>18250.15265</v>
+        <v>17645.230780000002</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752">
-        <v>2278.8962470000001</v>
+        <v>1708.882321</v>
       </c>
       <c r="B752">
-        <v>18260.033449999999</v>
+        <v>17659.45822</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753">
-        <v>2292.8055169999998</v>
+        <v>2269.0154459999999</v>
       </c>
       <c r="B753">
-        <v>18273.942719999999</v>
+        <v>18250.15265</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754">
-        <v>2309.5837980000001</v>
+        <v>2278.8962470000001</v>
       </c>
       <c r="B754">
-        <v>18290.721000000001</v>
+        <v>18260.033449999999</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755">
-        <v>2324.4969839999999</v>
+        <v>2292.8055169999998</v>
       </c>
       <c r="B755">
-        <v>18305.634190000001</v>
+        <v>18273.942719999999</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A756">
-        <v>2234.476701</v>
+        <v>2309.5837980000001</v>
       </c>
       <c r="B756">
-        <v>18317.629089999999</v>
+        <v>18290.721000000001</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757">
-        <v>2246.3261440000001</v>
+        <v>2324.4969839999999</v>
       </c>
       <c r="B757">
-        <v>18329.47853</v>
+        <v>18305.634190000001</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A758">
-        <v>2258.4655189999999</v>
+        <v>2234.476701</v>
       </c>
       <c r="B758">
-        <v>18341.617900000001</v>
+        <v>18317.629089999999</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A759">
-        <v>2273.211953</v>
+        <v>2246.3261440000001</v>
       </c>
       <c r="B759">
-        <v>18356.36434</v>
+        <v>18329.47853</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A760">
-        <v>2258.3682920000001</v>
+        <v>2258.4655189999999</v>
       </c>
       <c r="B760">
-        <v>18370.298790000001</v>
+        <v>18341.617900000001</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A761">
-        <v>2271.8797979999999</v>
+        <v>2273.211953</v>
       </c>
       <c r="B761">
-        <v>18383.810300000001</v>
+        <v>18356.36434</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A762">
-        <v>2281.82161</v>
+        <v>2258.3682920000001</v>
       </c>
       <c r="B762">
-        <v>18393.752110000001</v>
+        <v>18370.298790000001</v>
       </c>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A763">
-        <v>2295.043107</v>
+        <v>2271.8797979999999</v>
       </c>
       <c r="B763">
-        <v>18406.973610000001</v>
+        <v>18383.810300000001</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A764">
-        <v>2305.4897839999999</v>
+        <v>2281.82161</v>
       </c>
       <c r="B764">
-        <v>18417.420289999998</v>
+        <v>18393.752110000001</v>
       </c>
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A765">
-        <v>2266.7813930000002</v>
+        <v>2295.043107</v>
       </c>
       <c r="B765">
-        <v>18431.34116</v>
+        <v>18406.973610000001</v>
       </c>
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A766">
-        <v>2279.6419150000002</v>
+        <v>2305.4897839999999</v>
       </c>
       <c r="B766">
-        <v>18444.201679999998</v>
+        <v>18417.420289999998</v>
       </c>
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A767">
-        <v>2291.6583850000002</v>
+        <v>2266.7813930000002</v>
       </c>
       <c r="B767">
-        <v>18456.218150000001</v>
+        <v>18431.34116</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A768">
-        <v>2305.92209</v>
+        <v>2279.6419150000002</v>
       </c>
       <c r="B768">
-        <v>18470.48185</v>
+        <v>18444.201679999998</v>
       </c>
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A769">
-        <v>2316.4232539999998</v>
+        <v>2291.6583850000002</v>
       </c>
       <c r="B769">
-        <v>18480.98302</v>
+        <v>18456.218150000001</v>
       </c>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A770">
+        <v>2305.92209</v>
+      </c>
+      <c r="B770">
+        <v>18470.48185</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A771">
+        <v>2316.4232539999998</v>
+      </c>
+      <c r="B771">
+        <v>18480.98302</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A772">
         <v>2257.6769039999999</v>
       </c>
-      <c r="B770">
+      <c r="B772">
         <v>18496.532569999999</v>
       </c>
     </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.35"/>
-    <row r="772" spans="1:2" x14ac:dyDescent="0.35"/>
     <row r="773" spans="1:2" x14ac:dyDescent="0.35"/>
     <row r="774" spans="1:2" x14ac:dyDescent="0.35"/>
     <row r="775" spans="1:2" x14ac:dyDescent="0.35"/>
